--- a/df_log_20260308.xlsx
+++ b/df_log_20260308.xlsx
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경북플랫폼</t>
+          <t>경북도로관리사업소</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -505,12 +505,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>충북도로관리사업소</t>
+          <t>경북플랫폼</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -534,12 +534,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>경북도로관리사업소</t>
+          <t>충북도로관리사업소</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
+          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -563,12 +563,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경북도로관리사업소</t>
+          <t>강원도로관리사업소</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
+          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -592,12 +592,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>강원도로관리사업소</t>
+          <t>경북도로관리사업소</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -621,28 +621,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>울산시설관리공단</t>
+          <t>서울시설관리공단</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.uic.or.kr/notify/noti01.do</t>
+          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -654,40 +654,40 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>「2026년도 태화강수상스포츠센터 운영 용역」 사업자 선정 제안서 평가위원회 평가위원(후보자) 공개모집 공고</t>
+          <t>탄천1고가교 도장 보수공사 신기술·특허공법(강교도장) 선정 제안서 제출 안내 공고</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>인천광역시종합건설본부</t>
+          <t>울산시설관리공단</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
+          <t>https://www.uic.or.kr/notify/noti01.do</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,35 +699,35 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>공지2026년 신기술특허공법 선정위원회 평가결과 공개</t>
+          <t>「2026년도 태화강수상스포츠센터 운영 용역」 사업자 선정 제안서 평가위원회 평가위원(후보자) 공개모집 공고</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>경남도로관리사업소</t>
+          <t>인천광역시종합건설본부</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
+          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -744,12 +744,12 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>교량 인상공법 공법제안서 제출안내 공고(국도24호선 남강교 내진..</t>
+          <t>공지2026년 신기술특허공법 선정위원회 평가결과 공개</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
@@ -801,28 +801,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>인천시설관리공단</t>
+          <t>세종시설관리공단</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -834,40 +834,40 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[공지]신기술·특허 공법선정위원(후보자) 모집 공고(2026년 청라도시기반사업단 지하차도 및 교량 보수공사)</t>
+          <t>2025년 행복아파트 하반기 모집 입주자 및 예비입주자 선정결과 공고</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>세종시설관리공단</t>
+          <t>인천시설관리공단</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
+          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,35 +879,35 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025년 행복아파트 하반기 모집 입주자 및 예비입주자 선정결과 공고</t>
+          <t>[공지]신기술·특허 공법선정위원(후보자) 모집 공고(2026년 청라도시기반사업단 지하차도 및 교량 보수공사)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강원고시공고</t>
+          <t>부산시설관리공단</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/portal/bulletin/notification?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -924,35 +924,35 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026년 제1회 강원특별자치도 건축물미술작품 심의위원회 심의결과 공고</t>
+          <t>부산시민공원 잔디밭 도서관 실행 용역 제안서 평가위원 후보자 공개모집 공고</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>부산시설관리공단</t>
+          <t>강원고시공고</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
+          <t>https://state.gwd.go.kr/portal/bulletin/notification?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -969,33 +969,37 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>부산시민공원 잔디밭 도서관 실행 용역 제안서 평가위원 후보자 공개모집 공고</t>
+          <t>2026년 제1회 강원특별자치도 건축물미술작품 심의위원회 심의결과 공고</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대구시설관리공단</t>
+          <t>전남고시공고</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.dpfc.or.kr/sub.php?page_mode=1&amp;Page1=4&amp;Page2=3&amp;Page3=1&amp;Page4=2&amp;mode=list&amp;page_mode=&amp;board_name=notice&amp;search_field=total&amp;search_key=</t>
+          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -1010,7 +1014,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>�뱸��2������ CCTV��ġ �������� ����</t>
+          <t>2026년 국고보조사업 장애인 집합정보화 교육기관 선정결과 공고2026-03-06</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1067,28 +1071,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>전남고시공고</t>
+          <t>전북도로관리사업소</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1100,40 +1104,40 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026년 국고보조사업 장애인 집합정보화 교육기관 선정결과 공고2026-03-06</t>
+          <t>복흥119지역대 신축 건축공사</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>경기도_고양시</t>
+          <t>경남도로관리사업소</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
+          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1145,28 +1149,28 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>『2026년 고양IR데이 운영 용역』 제안서 평가위원(후보자)모집 공고</t>
+          <t>교량 인상공법 공법제안서 제출안내 공고(국도24호선 남강교 내진..</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>전북도로관리사업소</t>
+          <t>경기도_고양시</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1190,40 +1194,40 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>복흥119지역대 신축 건축공사</t>
+          <t>『2026년 고양IR데이 운영 용역』 제안서 평가위원(후보자)모집 공고</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>경남고시공고</t>
+          <t>전북고시공고</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1235,28 +1239,28 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026년 금원산산림자원관리소 숲해설 운영사업 제안서 평가결과 공개</t>
+          <t>복흥119지역대 신축 건축공사</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>전북고시공고</t>
+          <t>충북고시공고</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -1280,7 +1284,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>복흥119지역대 신축 건축공사</t>
+          <t>위임국도19호선 괴산 광덕리 도로확포장공사 신기술·특정공법 선정 안내 공고</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1337,23 +1341,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경기도_군포시</t>
+          <t>경남고시공고</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
+          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>90</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1370,12 +1374,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026년 주민참여예산 제안사업 공모 공고</t>
+          <t>2026년 금원산산림자원관리소 숲해설 운영사업 제안서 평가결과 공개</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -1427,23 +1431,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경기도_광명시</t>
+          <t>경기도_군포시</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
+          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>90</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1460,12 +1464,12 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>「2026년 액셀러레이팅 및 스타트업 챌린지」운영 용역 제안서 평가위원(후보자) 공개 모집 공고</t>
+          <t>2026년 주민참여예산 제안사업 공모 공고</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1546,28 +1550,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>충북고시공고</t>
+          <t>경기도_광명시</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
+          <t>https://www.gm.go.kr/pt/user/nftcBbs/BD_selectNftcBbsList.do?q_nftcBbsCode=1001&amp;q_rowPerPage=90</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1579,40 +1583,40 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>위임국도19호선 괴산 광덕리 도로확포장공사 신기술·특정공법 선정 안내 공고</t>
+          <t>「2026년 액셀러레이팅 및 스타트업 챌린지」운영 용역 제안서 평가위원(후보자) 공개 모집 공고</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경기도_오산시</t>
+          <t>울산광역시고시공고</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
+          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=5</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1624,12 +1628,12 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026년 다문화가족 자녀 방문학습지 대상자 모집 공고</t>
+          <t>수의계약 견적제출 공고 - 2026년 공공하수처리시설 보수공사 실시설계용역</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -1681,19 +1685,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>부산광역시고시공고</t>
+          <t>경기도_오산시</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.busan.go.kr/nbgosi?curPage=5</t>
+          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1702,7 +1706,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1714,35 +1718,35 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>「부산광역시 외국인주민정책 기본계획 수립 연구 용역」 제안서 기술능력(정성) 평가결과 공고</t>
+          <t>2026년 다문화가족 자녀 방문학습지 대상자 모집 공고</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경기도_하남시</t>
+          <t>부산광역시고시공고</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.hanam.go.kr/www/selectGosiList.do?key=171&amp;not_ancmt_se_code=01,04&amp;pageIndex=2</t>
+          <t>https://www.busan.go.kr/nbgosi?curPage=5</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1759,7 +1763,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026년 1월 정기분 등록면허세 반송분 공시송달</t>
+          <t>「부산광역시 외국인주민정책 기본계획 수립 연구 용역」 제안서 기술능력(정성) 평가결과 공고</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1771,16 +1775,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>충남도로관리사업소</t>
+          <t>경기도_동두천시</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
+          <t>https://www.ddc.go.kr/ddc/selectGosiList.do?key=340&amp;not_ancmt_se_code=04&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D33" t="n">
         <v>3</v>
@@ -1804,31 +1808,31 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>수의견적 제출 안내 공고(2026년 [논산]국지도68호 강경천교 보수보강공사)</t>
+          <t>가축(육용종계 및 육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경기도_화성시</t>
+          <t>충남도로관리사업소</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1837,7 +1841,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1849,35 +1853,35 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026년 매향리평화기념관 제2회 기획전시 설계·제작·설치 용역 제안서 ...</t>
+          <t>수의견적 제출 안내 공고(2026년 [논산]국지도68호 강경천교 보수보강공사)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>울산광역시고시공고</t>
+          <t>경기도_연천군</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=4</t>
+          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1887,18 +1891,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>수의계약 견적제출 공고 - 2026년 공공하수처리시설 보수공사 실시설계용역</t>
+          <t>연천 전곡리 유적 세계유산 잠정목록 등재를 위한 연구 용역 제안서 평가 결과 공개</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1910,23 +1910,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경기도_연천군</t>
+          <t>경기도_하남시</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
+          <t>https://www.hanam.go.kr/www/selectGosiList.do?key=171&amp;not_ancmt_se_code=01,04&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1943,7 +1943,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>연천 전곡리 유적 세계유산 잠정목록 등재를 위한 연구 용역 제안서 평가 결과 공개</t>
+          <t>2026년 1월 정기분 등록면허세 반송분 공시송달</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2000,23 +2000,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경기도_수원시</t>
+          <t>경기도_안산시</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=5</t>
+          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2033,7 +2033,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>민간임대주택에 관한 특별법 위반 과태료 체납 독촉 반송에 따른 공시송달 공고</t>
+          <t>신규주민등록증 통지서 반송자 공고(2009년 2월생)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2045,23 +2045,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>강원도_원주시</t>
+          <t>경기도_수원시</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
+          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=5</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2078,28 +2078,28 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>「2026년 혁신도시 문화행사(버스킹) 운영 대행 용역」기술제안서 평가결과 공개</t>
+          <t>민간임대주택에 관한 특별법 위반 과태료 체납 독촉 반송에 따른 공시송달 공고</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>강원도_삼척시</t>
+          <t>경기도_양평군</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
+          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
@@ -2123,7 +2123,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>고등 졸업학력 검정고시반 강사 모집 공고</t>
+          <t>2026년 양평군 조직진단 연구용역 제안서 평가위원회 평가결과 공고</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2135,23 +2135,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>강원도_인제군</t>
+          <t>강원도_삼척시</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
+          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>20</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2168,40 +2168,40 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026년 제1차 경관위원회 심의결과 공고</t>
+          <t>고등 졸업학력 검정고시반 강사 모집 공고</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경기도_과천시</t>
+          <t>경기도_화성시</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D42" t="n">
         <v>4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2213,7 +2213,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>도시계획시설(체육시설:승마경기장)사업 실시계획인가 전 열람 · 공고</t>
+          <t>2026년 매향리평화기념관 제2회 기획전시 설계·제작·설치 용역 제안서 ...</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2225,16 +2225,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>강원도_평창군</t>
+          <t>강원도_원주시</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.pc.go.kr/portal/government/government-notification</t>
+          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D43" t="n">
         <v>3</v>
@@ -2258,12 +2258,12 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>「2026년 평창군 자기주도학습 지원 사업 운영 용역」제안서 정성적 평가 결과 공고</t>
+          <t>「2026년 혁신도시 문화행사(버스킹) 운영 대행 용역」기술제안서 평가결과 공개</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -2315,23 +2315,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>강원도_영월군</t>
+          <t>강원도_인제군</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
+          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>20</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2348,28 +2348,28 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>「영월군 도로기반 지하시설물 전산화사업(산솔면)」 제안서 평가위원(후보자) 모집공고새글</t>
+          <t>2026년 제1차 경관위원회 심의결과 공고</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>경기도_양평군</t>
+          <t>강원도_영월군</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
+          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D46" t="n">
         <v>3</v>
@@ -2393,7 +2393,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026년 양평군 조직진단 연구용역 제안서 평가위원회 평가결과 공고</t>
+          <t>「영월군 도로기반 지하시설물 전산화사업(산솔면)」 제안서 평가위원(후보자) 모집공고새글</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2495,28 +2495,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경기도_시흥시</t>
+          <t>강원도_평창군</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
+          <t>https://www.pc.go.kr/portal/government/government-notification</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D49" t="n">
         <v>3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2528,35 +2528,35 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>가축 등에 대한 일시 이동중지 명령</t>
+          <t>「2026년 평창군 자기주도학습 지원 사업 운영 용역」제안서 정성적 평가 결과 공고</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>강원도_횡성군</t>
+          <t>경기도_과천시</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
+          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>20</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2573,7 +2573,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>154kV 북원주-횡성 기설송전선로 권원확보사업[4차] 전원개발사업 실시계획 변경승인 및 사업인정에 관한 주민 등의 의견청취 공고</t>
+          <t>도시계획시설(체육시설:승마경기장)사업 실시계획인가 전 열람 · 공고</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2585,23 +2585,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기도_포천시</t>
+          <t>경기도_시흥시</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
+          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2611,18 +2611,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>포천시 농업기술센터 공고 제2026-145호포천 고병원성AI 발생(축O종계장) 관련 방역대 내 농가 이동제한 및 소독명령</t>
+          <t>가축 등에 대한 일시 이동중지 명령</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -2679,12 +2675,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>충청도_제천시</t>
+          <t>강원도_횡성군</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
+          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2712,7 +2708,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>장선천 하천기본계획(재수립)을 위한 전략환경영향평가 항목 등의 결정내용 공고새글</t>
+          <t>154kV 북원주-횡성 기설송전선로 권원확보사업[4차] 전원개발사업 실시계획 변경승인 및 사업인정에 관한 주민 등의 의견청취 공고</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -2724,23 +2720,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>경기도_여주시</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
+          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2757,24 +2753,24 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>소규모 위험시설 지정 고시(주미동 소교량 외 28건)</t>
+          <t>2026년 마을공동체 주민제안 공모사업 선정...</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>충청도_옥천군</t>
+          <t>충청도_제천시</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.oc.go.kr/www/selectBbsNttList.do?bbsNo=40&amp;key=236&amp;pageIndex=2</t>
+          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2802,7 +2798,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>가축 등에 대한 일시 이동중지 명령(육계 및 육용종계)새글</t>
+          <t>장선천 하천기본계획(재수립)을 위한 전략환경영향평가 항목 등의 결정내용 공고새글</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -2814,23 +2810,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>충청도_옥천군</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
+          <t>https://www.oc.go.kr/www/selectBbsNttList.do?bbsNo=40&amp;key=236&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2847,7 +2843,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>공주시 충남형 농촌리브투게더 신풍지구 임대주택 입주자 추가 모집 공고(8차)</t>
+          <t>가축 등에 대한 일시 이동중지 명령(육계 및 육용종계)새글</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -2859,68 +2855,60 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>충청도_계룡시</t>
+          <t>대구시설관리공단</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
+          <t>https://www.dpfc.or.kr/sub.php?page_mode=board&amp;Page1=6&amp;Page2=5&amp;Page3=1&amp;Page4=0&amp;sub_mode=p</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026년도 농작업 보호장비 지원사업 알림</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>경기도_여주시</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=3</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2937,40 +2925,40 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026년 마을공동체 주민제안 공모사업 선정...</t>
+          <t>소규모 위험시설 지정 고시(주미동 소교량 외 28건)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>충청도_보령시</t>
+          <t>충청도_계룡시</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
+          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>20</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2982,88 +2970,88 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>가축(육용종계, 육계) 등에 대한 일시이동중지(Standstill) 명령 알림(경기 포천 HPAI)</t>
+          <t>2026년도 농작업 보호장비 지원사업 알림</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>충청도_부여군</t>
+          <t>전라도_남원시</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
+          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>「부여군 매장문화재 유존지역 정보고도화 사업 지도 제작 및 DB 구축 용역」 제안서 평가위원(후보자) 모집 공고</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>2024-04-17</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>전라도_남원시</t>
+          <t>충청도_예산군</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>구)충남방적부지개발사업 기본구상 및 타당성조사용역 제안서 평가결과</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3073,7 +3061,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3101,35 +3089,35 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>구)충남방적부지개발사업 기본구상 및 타당성조사용역 제안서 평가결과</t>
+          <t>2026년 봉수산 자연휴양림 데크보행로 교체사업 실시설계용역 수의(2인 이상) 견적제출 안내공고</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>충청도_예산군</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3146,40 +3134,40 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026년 봉수산 자연휴양림 데크보행로 교체사업 실시설계용역 수의(2인 이상) 견적제출 안내공고</t>
+          <t>공주시 충남형 농촌리브투게더 신풍지구 임대주택 입주자 추가 모집 공고(8차)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>전라도_부안군</t>
+          <t>충청도_부여군</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
+          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3191,40 +3179,40 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>도로기반 지하시설물 전산화 확산사업 제안서 평가위원(후보자) 모집 공고</t>
+          <t>「부여군 매장문화재 유존지역 정보고도화 사업 지도 제작 및 DB 구축 용역」 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2024-04-17</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>충청도_금산군</t>
+          <t>충청도_보령시</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
+          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>20계속</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3236,28 +3224,28 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[일반공고]2026년 금산군 군민리포터 모집 공고</t>
+          <t>가축(육용종계, 육계) 등에 대한 일시이동중지(Standstill) 명령 알림(경기 포천 HPAI)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>20계속</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>경기도_안산시</t>
+          <t>강원도_홍천군</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
+          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D66" t="n">
         <v>3</v>
@@ -3281,7 +3269,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>신규주민등록증 통지서 반송자 공고(2009년 2월생)</t>
+          <t>지적측량기준점(도근점) 성과 고시</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3293,28 +3281,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>전라도_김제시</t>
+          <t>전라도_강진군</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3326,31 +3314,31 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>자동차 편취말소 예고 통지에 따른 고시공고</t>
+          <t>전기사업 양수인가 공고(해든 태양광발전소)새로운글</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>전라도_곡성군</t>
+          <t>전라도_부안군</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
+          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3359,7 +3347,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3371,7 +3359,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>도로명주소 고시(2026-03-06)</t>
+          <t>도로기반 지하시설물 전산화 확산사업 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -3383,28 +3371,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>충청도_청주시</t>
+          <t>전라도_곡성군</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=5</t>
+          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D69" t="n">
         <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3416,40 +3404,40 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>통장 선정 주민투표 공고(28통)</t>
+          <t>도로명주소 고시(2026-03-06)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>전라도_무안군</t>
+          <t>충청도_금산군</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
+          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20계속</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3461,40 +3449,40 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026 신도시주민 농업.농촌 체험 활동 추가 모집공고</t>
+          <t>[일반공고]2026년 금산군 군민리포터 모집 공고</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20계속</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>전라도_구례군</t>
+          <t>전라도_김제시</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=1</t>
+          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>10</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3506,31 +3494,31 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026년 입식테이블 및 경사로 설치 지원 사업 모집(신청) 공고</t>
+          <t>자동차 편취말소 예고 통지에 따른 고시공고</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>충청도_음성군</t>
+          <t>전라도_구례군</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
+          <t>https://www.gurye.go.kr/board/GosiList.do?not_ancmt_se_code=01,04,06,07&amp;menuNo=115004002001&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3539,7 +3527,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3551,28 +3539,28 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>음성 그린에너지 스마트농업타운 투자선도지구 출자타당성 검토 용역 제안서 ...</t>
+          <t>2026년 입식테이블 및 경사로 설치 지원 사업 모집(신청) 공고</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>강원도_홍천군</t>
+          <t>전라도_무안군</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
+          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D73" t="n">
         <v>3</v>
@@ -3596,7 +3584,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>지적측량기준점(도근점) 성과 고시</t>
+          <t>2026 신도시주민 농업.농촌 체험 활동 추가 모집공고</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -3608,73 +3596,77 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>전라도_고창군</t>
+          <t>경기도_포천시</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
+          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[43425]「고창갯벌 세계유산 OUV 공감 콘텐츠 용역」 제안서 평가 결과 공고첨부파일 있음</t>
+          <t>포천시 농업기술센터 공고 제2026-145호포천 고병원성AI 발생(축O종계장) 관련 방역대 내 농가 이동제한 및 소독명령</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>대구광역시고시공고</t>
+          <t>충청도_청주시</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
+          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3686,28 +3678,28 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>「2026년 대구광역시 항공사진 촬영 용역」 제안서 평가위원회 평가위원(후보자) 모집 공고문</t>
+          <t>통장 선정 주민투표 공고(28통)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>전라도_순천시</t>
+          <t>전라도_진도군</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=4</t>
+          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D76" t="n">
         <v>3</v>
@@ -3731,7 +3723,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026년 순천만국가정원 관객참여형 디지털인형극 운영 용역 제안서 평가 ...</t>
+          <t>[고시]진도 군관리계획(문화공원 및 공원조성계획) 결정(변경) 지형도면 고시</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3743,16 +3735,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>전라도_진도군</t>
+          <t>충청도_음성군</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
+          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D77" t="n">
         <v>3</v>
@@ -3776,7 +3768,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[고시]진도 군관리계획(문화공원 및 공원조성계획) 결정(변경) 지형도면 고시</t>
+          <t>음성 그린에너지 스마트농업타운 투자선도지구 출자타당성 검토 용역 제안서 ...</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3788,28 +3780,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>전라도_고창군</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
+          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D78" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3821,77 +3813,85 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>제9회 전국동시지방선거 공정선거지원단(선거) 모집 안내</t>
+          <t>[43425]「고창갯벌 세계유산 OUV 공감 콘텐츠 용역」 제안서 평가 결과 공고첨부파일 있음</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>서울시설관리공단</t>
+          <t>전라도_완도군</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=notice</t>
+          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2026년 보길면 윤선도원림 경관조성 및 관리 기간제근로자 최종합격자 공...새로운글</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>전라도_완도군</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
+          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3903,28 +3903,28 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026년 보길면 윤선도원림 경관조성 및 관리 기간제근로자 최종합격자 공...새로운글</t>
+          <t>제9회 전국동시지방선거 공정선거지원단(선거) 모집 안내</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>전라도_영광군</t>
+          <t>전라도_순천시</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
+          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=4</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D81" t="n">
         <v>3</v>
@@ -3948,7 +3948,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>영광읍 농촌중심지활성화사업 기본계획 승인 고시</t>
+          <t>2026년 순천만국가정원 관객참여형 디지털인형극 운영 용역 제안서 평가 ...</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -3960,23 +3960,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>전라도_해남군</t>
+          <t>전라도_영광군</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
+          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D82" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3993,35 +3993,35 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026년 전남형 동행 일자리사업 사업제안서(수행기관) 공모...파일</t>
+          <t>영광읍 농촌중심지활성화사업 기본계획 승인 고시</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>경상도_상주시</t>
+          <t>전라도_해남군</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
+          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>100</v>
       </c>
       <c r="D83" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4038,12 +4038,12 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026년 상반기 시민주도 평생교육강좌 제안 추가 모집 공고</t>
+          <t>2026년 전남형 동행 일자리사업 사업제안서(수행기관) 공모...파일</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
@@ -4095,35 +4095,47 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>전라도_보성군</t>
+          <t>경상도_상주시</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
+          <t>https://www.sangju.go.kr/dong/page/15910/11235.tc</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>찾아가는 장난감도서관 「누리빵빵」 시범운영 정차지 변경사항 안내</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4169,78 +4181,102 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>경상도_영주시</t>
+          <t>경상도_상주시</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
+          <t>https://www.sangju.go.kr/page/10297/10606.tc?mn=10297&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2026년 상반기 시민주도 평생교육강좌 제안 추가 모집 공고</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>대구광역시고시공고</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>「2026년 대구광역시 항공사진 촬영 용역」 제안서 평가위원회 평가위원(후보자) 모집 공고문</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>경상도_영주시</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/bbs/list.do?ptIdx=568&amp;mId=0301030000</t>
+          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4253,12 +4289,12 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -4268,28 +4304,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경상도_상주시</t>
+          <t>충청도_홍성군</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.sangju.go.kr/dong/page/15910/11235.tc</t>
+          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4301,57 +4337,69 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>찾아가는 장난감도서관 「누리빵빵」 시범운영 정차지 변경사항 안내</t>
+          <t>전문건설업 등록(신규, 업종추가) 공고</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>경상도_군위군</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
+          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>도로명주소 고시</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>충청도_서산시</t>
+          <t>전라도_보성군</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
+          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4364,12 +4412,12 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4408,61 +4456,73 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>충청도_서산시</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
+          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>「서산시 2차 스마트도시계획 수립 용역」의 제안서 평가위원회 결과 공고</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>경상도_경주시</t>
+          <t>전라도_광양시</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=3</t>
+          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D95" t="n">
         <v>3</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4474,171 +4534,163 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>대곡금척 자연재해위험개선지구 정비사업 실시계획(변경) 공고</t>
+          <t>2026년 숲생태관리인(숲해설가) 채용 공고</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>전라도_영암군</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
+          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>도로명주소 부여 고시</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경상도_군위군</t>
+          <t>경상도_김천시</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
+          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>도로명주소 고시</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경기도_동두천시</t>
+          <t>경상도_창원시_의창구</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.ddc.go.kr/ddc/contents.do?key=340</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>10</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>가축(육용종계 및 육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
+          <t>[의창구 팔룡동] 여성민방위 기동대 민방위 비상급수 시설 점검</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경상도_창원시_의창구</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D99" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4650,73 +4702,85 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[의창구 팔룡동] 여성민방위 기동대 민방위 비상급수 시설 점검</t>
+          <t>2026년 창원시 기후대기 개선사업 한눈에 보기새 글</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>경상도_창원시_성산구</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>성산구,「2026년 재가의료급여 사업」업무 협약체결</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>충청도_홍성군</t>
+          <t>경상도_창원시_마산합포구</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4728,69 +4792,57 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>전문건설업 등록(신규, 업종추가) 공고</t>
+          <t>마산합포구, 체납차량 번호판 집중 영치기간 운영새 글</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>경상도_창원시_성산구</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
+          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>9</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>성산구,「2026년 재가의료급여 사업」업무 협약체결</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>경상도_창원시_진해구</t>
+          <t>경상도_창원시_마산회원구</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -4801,7 +4853,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4818,7 +4870,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>(진해구 태백동) 우리동네 한바퀴 지킴이단 순찰활동 실시새 글</t>
+          <t>(마산회원구 가정복지과) 한눈에, 한 손에, 한부모가족 복지안내서 제작·배부새 글</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -4830,28 +4882,28 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산합포구</t>
+          <t>경상도_창원시_진해구</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>10</v>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4863,113 +4915,113 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>마산합포구, 체납차량 번호판 집중 영치기간 운영새 글</t>
+          <t>(진해구 태백동) 우리동네 한바퀴 지킴이단 순찰활동 실시새 글</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산회원구</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
+          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>8</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>(마산회원구 가정복지과) 한눈에, 한 손에, 한부모가족 복지안내서 제작·배부새 글</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>경상도_안동시</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=5</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>『덕동생활폐기물매립장 2단계 조성사업』공법선정을 위한 공법선정위원회 평가위원(후보자) 모집 공고</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경상도_거제시</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
+          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4986,73 +5038,81 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>정수장 일일수질검사 결과 안내(2026.3.6.)</t>
+          <t>「거제식물원 열린관광 콘텐츠 기획 및 구축 용역」 제안서 평가결과 공고</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>전라도_강진군</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=2</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>[종합소식]양육비 선지급제 안내새 글</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D109" t="n">
         <v>3</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5064,7 +5124,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026년 창원시 기후대기 개선사업 한눈에 보기새 글</t>
+          <t>「주촌면 농촌중심지 활성화사업 기본계획수립 용역」제안서 평가결과 공고</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -5076,12 +5136,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>전라도_광양시</t>
+          <t>경상도_사천시</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
+          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -5092,12 +5152,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5109,121 +5169,101 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026년 숲생태관리인(숲해설가) 채용 공고</t>
+          <t>[사천시 공고 제2026-449호]담배소매인(사망자)직권취소 및 지정신청 공고새 글</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>7</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>2025년 성과관리 평가결과 공개</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=2</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>[종합소식]양육비 선지급제 안내새 글</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
+          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5240,40 +5280,40 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>남영덕 하이패스IC(고속국도 65호선) 추가설치 타당성조사 용역 제안서 평가위원(후보자) 모집 공고</t>
+          <t>2025년 성과관리 평가결과 공개</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>경상도_거제시</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
+          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D114" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20새글</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5285,40 +5325,40 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>「거제식물원 열린관광 콘텐츠 기획 및 구축 용역」 제안서 평가결과 공고</t>
+          <t>[일자리ㆍ기업]「2026년 소상공인 온라인 입점 지원사업」  참여 소상공인 모집 공고 안내새글</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>20새글</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>경상도_사천시</t>
+          <t>경상도_남해군_남해읍</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5330,12 +5370,12 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[사천시 공고 제2026-449호]담배소매인(사망자)직권취소 및 지정신청 공고새 글</t>
+          <t>2026년 농어촌 기본소득 지원 남해읍 기간제 근로자 채용 공고(수정)</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -5371,19 +5411,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>경상도_남해군_남해읍</t>
+          <t>경상도_남해군_이동면</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%ED%95%B4%EC%9D%8D&amp;pageCd=WW0512010103&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>10</v>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -5392,7 +5432,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5404,40 +5444,40 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026년 농어촌 기본소득 지원 남해읍 기간제 근로자 채용 공고(수정)</t>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(이동면)</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>경상도_남해군_이동면</t>
+          <t>경상도_의령군</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
+          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>10</v>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5449,40 +5489,40 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(이동면)</t>
+          <t>전문건설업 신규등록 공고</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>경상도_의령군</t>
+          <t>경상도_남해군_삼동면</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>10</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5494,24 +5534,24 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>전문건설업 신규등록 공고</t>
+          <t>2026년 삼동다락생활문화센터 프로그램 수강생 모집 공고(수정)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>경상도_김천시</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
+          <t>https://www.yc.go.kr/portal/contents.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5539,28 +5579,28 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_남해군_미조면</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=5</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5572,59 +5612,47 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>『덕동생활폐기물매립장 2단계 조성사업』공법선정을 위한 공법선정위원회 평가위원(후보자) 모집 공고</t>
+          <t>2026년 미조면 취약해안폐기물 대응사업 채용공고</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>경상도_남해군_삼동면</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
+          <t>https://www.yc.go.kr/portal/contents.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>9</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>2026년 삼동다락생활문화센터 프로그램 수강생 모집 공고(수정)</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5658,28 +5686,28 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>경상도_남해군_미조면</t>
+          <t>경상도_남해군_남면</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>10</v>
       </c>
       <c r="D124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5691,12 +5719,12 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>2026년 미조면 취약해안폐기물 대응사업 채용공고</t>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(남면)</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
@@ -5793,28 +5821,28 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>경상도_남해군_남면</t>
+          <t>경상도_통영시</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
+          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D127" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5826,73 +5854,85 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(남면)</t>
+          <t>통영 수산업・어촌 발전 기본계획 수립 연구용역 제안서 평가위원회 결과 공고</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>경상도_고성군</t>
+          <t>경상도_남해군_설천면</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(설천면)</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>경상도_통영시</t>
+          <t>경상도_남해군_창선면</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5904,40 +5944,40 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>통영 수산업・어촌 발전 기본계획 수립 연구용역 제안서 평가위원회 결과 공고</t>
+          <t>2026년 창선면 해양쓰레기 정화사업(구 바다환경지킴이)기간제근로자 채용 안내</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>경상도_하동군</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
+          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D130" t="n">
         <v>3</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5949,7 +5989,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>「주촌면 농촌중심지 활성화사업 기본계획수립 용역」제안서 평가결과 공고</t>
+          <t>경기도 포천시 AI발생 관련 가축(육용종계,육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -5961,28 +6001,28 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>경상도_남해군_설천면</t>
+          <t>경상도_거창군</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
+          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5994,47 +6034,59 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(설천면)</t>
+          <t>제292회 거창군의회 임시회 집회 공고</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>경상도_진주시</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
+          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>밀양시 2030's 미래농업 프로젝트 추진계획 용역 제안서 평...</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6072,68 +6124,56 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>경상도_남해군_창선면</t>
+          <t>경상도_안동시</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
+          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>9</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>2026년 창선면 해양쓰레기 정화사업(구 바다환경지킴이)기간제근로자 채용 안내</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>전라도_영암군</t>
+          <t>경상도_경주시</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
+          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=3</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6143,14 +6183,18 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>도로명주소 부여 고시</t>
+          <t>대곡금척 자연재해위험개선지구 정비사업 실시계획(변경) 공고</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -6162,57 +6206,45 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>경상도_하동군</t>
+          <t>경상도_고성군</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
+          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>경기도 포천시 AI발생 관련 가축(육용종계,육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>경상도_창녕군</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
+          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -6240,23 +6272,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>경상도_거창군</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
+          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6266,31 +6298,35 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>제292회 거창군의회 임시회 집회 공고</t>
+          <t>남영덕 하이패스IC(고속국도 65호선) 추가설치 타당성조사 용역 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>경상도_문경시</t>
+          <t>경상도_진주시</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
+          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -6318,61 +6354,45 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>경상도_창녕군</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
+          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>타임아웃</t>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>양산 매장유산 유존지역 정보고도화 사업(비도심) 제안서 평가위원(후보자) 공개모집 공고</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>경상도_문경시</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
+          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -6383,105 +6403,129 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Zero-Selector성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>2023년 함평군 지적재조사사업 완료 공람·공고</t>
+          <t>「문경시 문화예술회관 안전난간 설치사업」신기술・특허공법 선정 기술제안서 제출기한 연장 안내 공고</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000</t>
+          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
+          <t>실패(타임아웃)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+          <t>타임아웃</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>양산 매장유산 유존지역 정보고도화 사업(비도심) 제안서 평가위원(후보자) 공개모집 공고</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000</t>
+          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: div.board-list-wrap)</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>테이블 없음: div.board-list-wrap</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+          <t>Zero-Selector성공</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2023년 함평군 지적재조사사업 완료 공람·공고</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6491,7 +6535,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/news</t>
+          <t>https://www.gumc.or.kr/news/bidding</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -6520,7 +6564,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/bidding</t>
+          <t>https://www.gumc.or.kr/news/news</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -6614,78 +6658,98 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>경기도_수원_팔달구</t>
+          <t>경기도감사위원회고시공고</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
+          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>신기술·특허 공법 선정 안내 정정 공고(묵현천 지방하천 정비사업)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>경기도감사위원회고시공고</t>
+          <t>경기도_수원_팔달구</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
+          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>장애인전용주차구역 주차위반 압류통지 반송분 공시송달 공고</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>경기도_수원_장안구</t>
+          <t>경기도_수원_권선구</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -6717,7 +6781,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>불법옥외광고물 자진정비 시정명령 사전안내 반송에 따른 공시송달 공고</t>
+          <t>이륜자동차 정기검사 신청기간 경과 알림 및 명령서 반송분 공시송달 공고</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -6729,12 +6793,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>경기도_수원_권선구</t>
+          <t>경기도_수원_장안구</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -6766,7 +6830,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>이륜자동차 정기검사 신청기간 경과 알림 및 명령서 반송분 공시송달 공고</t>
+          <t>불법옥외광고물 자진정비 시정명령 사전안내 반송에 따른 공시송달 공고</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -6840,7 +6904,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6857,63 +6921,75 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2084</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>경기도_부천시</t>
+          <t>광주광역시고시공고</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
+          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table tbody tr)</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>테이블 없음: table tbody tr</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>신기술·특허공법 제안 재공고[광주도시철도 2호선 2단계 기본 및 실시설계용역(토목/건축 설계2공구)]</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>광주광역시고시공고</t>
+          <t>경기도_광주시</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
+          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6923,42 +6999,46 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
+          <t>실패(타임아웃)</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>타임아웃</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>신기술·특허공법 제안 재공고[광주도시철도 2호선 2단계 기본 및 실시설계용역(토목/건축 설계2공구)]</t>
+          <t>『2026년 광주시 장애인평생학습센터 강의안 제안』공모</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>경기도_광주시</t>
+          <t>대전광역시고시공고</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
+          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6968,23 +7048,19 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>『2026년 광주시 장애인평생학습센터 강의안 제안』공모</t>
+          <t>제안서 평가위원 공개모집 재공고(성북동체육공원 파크골프장 조성 타당성 조사 및 기본계획 수립용역)</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -7036,23 +7112,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>대전광역시고시공고</t>
+          <t>경기도_용인시처인구</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
+          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7069,7 +7145,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>제안서 평가위원 공개모집 재공고(성북동체육공원 파크골프장 조성 타당성 조사 및 기본계획 수립용역)</t>
+          <t>무단 방치자전거 보관 및 처분 공고</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -7081,23 +7157,23 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>경기도_안양시</t>
+          <t>경기고시공고</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
+          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=5</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7114,35 +7190,35 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>「박달동 및 인덕원동 하수도정비 중점관리지역 도시침수예방사업」공법선정평가위원회 평가위원(후보자) 공개모집 공고</t>
+          <t>『3기 신도시 리츠 도입 연구용역 2건』제안서 평가위원 후보자 공개모집</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>경기도_성남시중원구</t>
+          <t>경기도_부천시</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7159,7 +7235,7 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>무단방치 이륜차 자진처리명령서 공시송달 및 강제처리(폐차) 공고</t>
+          <t>2026년 마을공동체 활동매니저 합격자 공고</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -7171,16 +7247,16 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>경기도_용인시처인구</t>
+          <t>경기도_성남시</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
+          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D161" t="n">
         <v>1</v>
@@ -7197,18 +7273,14 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table.boardDefalut tbo)</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>테이블 없음: table.boardDefalut tbody tr</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>무단 방치자전거 보관 및 처분 공고</t>
+          <t>도로명주소(건물번호) 부여 고시</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -7261,23 +7333,23 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>경기고시공고</t>
+          <t>경기도_안양시</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=5</t>
+          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7294,35 +7366,35 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>『3기 신도시 리츠 도입 연구용역 2건』제안서 평가위원 후보자 공개모집</t>
+          <t>「박달동 및 인덕원동 하수도정비 중점관리지역 도시침수예방사업」공법선정평가위원회 평가위원(후보자) 공개모집 공고</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>경기도_성남시</t>
+          <t>경기도_성남시중원구</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7339,7 +7411,7 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>도로명주소(건물번호) 부여 고시</t>
+          <t>무단방치 이륜차 자진처리명령서 공시송달 및 강제처리(폐차) 공고</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -7396,56 +7468,68 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>경기도_의정부시</t>
+          <t>경기도_성남시분당구</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>소액수의 견적제출 안내 공고-가로수 수형관리공사(판교지구 등)</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>경기도_성남시분당구</t>
+          <t>강원도_동해시</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
+          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7462,35 +7546,35 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>소액수의 견적제출 안내 공고-가로수 수형관리공사(판교지구 등)</t>
+          <t>「동해시 교육발전 중장기 기본계획 수립 연구 용역」 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>강원도_동해시</t>
+          <t>경기도_의정부시</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
+          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D168" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7507,12 +7591,12 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>「동해시 교육발전 중장기 기본계획 수립 연구 용역」 제안서 평가위원(후보자) 모집 공고</t>
+          <t>도로점용(굴착)허가 내용 공고[제2026-의정부동점용(굴착)-2호, 대○이○에○, 가능동 15-484(가능동 15-79)]</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -7642,101 +7726,101 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>강원도_속초시</t>
+          <t>강원도_양구군</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
+          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>속초 도시계획시설(도로: 중로3-35호선) 실시계획인가(변경) 고시</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>강원도_양구군</t>
+          <t>강원도_속초시</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
+          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
-      </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>속초 도시계획시설(도로: 중로3-35호선) 실시계획인가(변경) 고시</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>충청도_괴산군</t>
+          <t>강원도_화천군</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>10</v>
       </c>
       <c r="D174" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7753,7 +7837,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>도로명주소 고시</t>
+          <t>2026년 실외사육견 중성화 지원 사업시행자(동물병원) 모집 공고</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -7765,22 +7849,30 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>강원도_화천군</t>
+          <t>경기도_안성시</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
+          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t>성공</t>
@@ -7788,29 +7880,37 @@
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>공도 도시계획시설(공공ㆍ문화체육시설: 문화 및 사회복지시설-공도시민청) 실시계획(변경)작성 고시</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>강원도_양양군</t>
+          <t>충청도_괴산군</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D176" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7827,7 +7927,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>「행정재산 실태조사 및 공유재산 통합 DB구축 용역」 제안서 평가위원회 평가 결과 공고</t>
+          <t>도로명주소 고시</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -7868,16 +7968,16 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>경기도_안성시</t>
+          <t>강원도_양양군</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
+          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D178" t="n">
         <v>3</v>
@@ -7901,7 +8001,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>공도 도시계획시설(공공ㆍ문화체육시설: 문화 및 사회복지시설-공도시민청) 실시계획(변경)작성 고시</t>
+          <t>「행정재산 실태조사 및 공유재산 통합 DB구축 용역」 제안서 평가위원회 평가 결과 공고</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -7913,23 +8013,23 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>강원도_정선군</t>
+          <t>경기도_파주시</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7939,18 +8039,14 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>주택건설사업계획 승인 고시 [SG아파트_세기건설(주)]</t>
+          <t>파랑해 이벤트 Vol. 1 「내가 그린 파랑, 띠-부 스티커가로 태어나다!」 새학기 맞이 공모이벤트N</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -7962,16 +8058,16 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>경기도_파주시</t>
+          <t>충청도_청주시_흥덕구</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D180" t="n">
         <v>3</v>
@@ -7995,7 +8091,7 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>파랑해 이벤트 Vol. 1 「내가 그린 파랑, 띠-부 스티커가로 태어나다!」 새학기 맞이 공모이벤트N</t>
+          <t>압류자동차 공매 공고</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -8007,23 +8103,23 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>충청도_청주시_흥덕구</t>
+          <t>강원도_정선군</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
+          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>10</v>
       </c>
       <c r="D181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8033,14 +8129,18 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr"/>
+          <t>실패(타임아웃)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>타임아웃</t>
+        </is>
+      </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>압류자동차 공매 공고</t>
+          <t>주택건설사업계획 승인 고시 [SG아파트_세기건설(주)]</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -8052,28 +8152,28 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>충청도_보은군</t>
+          <t>충청도_단양군</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
+          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C182" t="n">
         <v>10</v>
       </c>
       <c r="D182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -8085,40 +8185,40 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>경기 포천 육용종계농장 고병원성 조류인플루엔자 발생관련 가축(육용종계, 육계) 등에 대한 일시이동중지 명령 알림</t>
+          <t>2026년 지적재조사사업 측량·조사 등의 위탁고시</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>충청도_영동군</t>
+          <t>충청도_보은군</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
+          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D183" t="n">
         <v>3</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8130,57 +8230,69 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>금계천 금계지구 지방하천 정비사업 공법선정 심의위원회 평가결과 공고</t>
+          <t>경기 포천 육용종계농장 고병원성 조류인플루엔자 발생관련 가축(육용종계, 육계) 등에 대한 일시이동중지 명령 알림</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>충청도_증평군</t>
+          <t>충청도_영동군</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
+          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
-      </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: form &gt; table:nth-child)</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>테이블 없음: form &gt; table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table &gt; tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>금계천 금계지구 지방하천 정비사업 공법선정 심의위원회 평가결과 공고</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>충청도_논산시</t>
+          <t>충청도_증평군</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
+          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -8208,12 +8320,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>충청도_당진시</t>
+          <t>충청도_진천군</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
+          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -8241,73 +8353,61 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>충청도_단양군</t>
+          <t>충청도_당진시</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr"/>
+          <t>실패(타임아웃)</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>타임아웃</t>
+        </is>
+      </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>2026년 지적재조사사업 측량·조사 등의 위탁고시</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>강원도_춘천시</t>
+          <t>충청도_서천군</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
+          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -8319,147 +8419,135 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>강촌분구 외 5개소 노후하수관로 정비사업 실시설계용역 사업 집행계획 및 사업수행능력평가서 제출안내 공고</t>
+          <t>도로명주소 고시</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>충청도_진천군</t>
+          <t>충청도_청양군</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
+          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>3</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>『구암저수지 둘레길 조성사업』 신기술·특허공법 선정 공법제안서 제출안내 ...</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>충청도_청양군</t>
+          <t>충청도_태안군</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
+          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>3</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>2026년 환경개선부담금 부과 관련 개인정보 제3자 위탁사항 알림</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>충청도_태안군</t>
+          <t>강원도_춘천시</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
-      </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>강촌분구 외 5개소 노후하수관로 정비사업 실시설계용역 사업 집행계획 및 사업수행능력평가서 제출안내 공고</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>전라도_군산시</t>
+          <t>전라도_전주시</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -8472,12 +8560,12 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>타임아웃</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -8487,52 +8575,64 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>충청도_서천군</t>
+          <t>충청도_천안시</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
-      </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table[width='639'] tbo)</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>테이블 없음: table[width='639'] tbody tr:has(td[onclick*='searchDetail'])</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>「풍서천 재해복구사업(개선)」재난안전신기술 공법선정을 위한 기술제안서 제...</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>충청도_천안시</t>
+          <t>충청도_아산시</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
+          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C194" t="n">
         <v>30</v>
       </c>
       <c r="D194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -8541,7 +8641,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8553,7 +8653,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>「풍서천 재해복구사업(개선)」재난안전신기술 공법선정을 위한 기술제안서 제...</t>
+          <t>2026년 아산 국가유산 야행 행사대행 용역 제안서 평가결과 및 우선협상...</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -8565,118 +8665,122 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>충청도_아산시</t>
+          <t>전라도_군산시</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
+          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>3</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
+          <t>실패(테이블 없음: table[summary='고시공고 목록)</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>테이블 없음: table[summary='고시공고 목록'] tbody tr[bgcolor]</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>2026년 아산 국가유산 야행 행사대행 용역 제안서 평가결과 및 우선협상...</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>전라도_전주시</t>
+          <t>충청도_청주시_상당구</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
-      </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>학대피해아동쉼터 운영 수탁자 선정 심의결과 공고</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>충청도_청주시_상당구</t>
+          <t>전라도_익산시</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
+          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(27) &gt; )</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(27) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>학대피해아동쉼터 운영 수탁자 선정 심의결과 공고</t>
+          <t>용동면 기초생활거점조성사업(2단계) 기본계획 및 시행계획 승인 고시</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -8688,35 +8792,47 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>전라도_익산시</t>
+          <t>충청도_논산시</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
+          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
-      </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>지적기준점(도근점) 성과고시(세계좌표 3점)</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8730,104 +8846,116 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>북서부재생활성화지역(복흥·쌍치·구림) 기본계획 수립 용역 제안서 평가위원 모집공고</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>전라도_진안군</t>
+          <t>전라도_장수군</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
-      </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>「장수군 이종무 장군 재조명 및 기념사업 지원에 관한 조례안」입법예고</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>전라도_장수군</t>
+          <t>전라도_진안군</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
+          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>3</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>「장수군 이종무 장군 재조명 및 기념사업 지원에 관한 조례안」입법예고</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8910,23 +9038,23 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>전라도_목포시</t>
+          <t>전라도_정읍시</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
+          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8936,14 +9064,18 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>공유수면 점용사용 변경허가 고시새로운글</t>
+          <t>칠보면 와우제 보수보강공사 긴급 입찰공고</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -8955,23 +9087,23 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>전라도_완주군</t>
+          <t>전라도_무주군</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://eminwon.wanju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C205" t="n">
         <v>30</v>
       </c>
       <c r="D205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -8988,7 +9120,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>2026년 저소득층 그린리모델링 사업 공고</t>
+          <t>2026년 무주군 보육정책위원회 심의결과 공고</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -9000,50 +9132,61 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>전라도_담양군</t>
+          <t>전라도_목포시</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
+          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
-      </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>실패(Alert Text: /eminwon/getSearch)</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Alert Text: /eminwon/getSearchList 페이징 오류
-Message: unexpected alert open: {Alert text : /eminwon/get</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>공유수면 점용사용 변경허가 고시새로운글</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>전라도_장흥군</t>
+          <t>전라도_완주군</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
+          <t>https://eminwon.wanju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D207" t="n">
         <v>4</v>
@@ -9067,35 +9210,35 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>「장흥 쓰레기위생매립장 침출수처리시설 개선사업」 침출수처리 공법..</t>
+          <t>2026년 저소득층 그린리모델링 사업 공고</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>전라도_정읍시</t>
+          <t>전라도_장흥군</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9112,12 +9255,12 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>칠보면 와우제 보수보강공사 긴급 입찰공고</t>
+          <t>「장흥 쓰레기위생매립장 침출수처리시설 개선사업」 침출수처리 공법..</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
@@ -9214,28 +9357,28 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>전라도_담양군</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
+          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D211" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -9247,40 +9390,40 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>포항시 공공하수처리시설 방류수 수질결과 공개(2026.2.28기준)</t>
+          <t>전문건설업 자료제출 공문 반송에 따른 공시송달 공고</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>전라도_화순군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
+          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D212" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -9292,34 +9435,42 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>제279회 화순군의회 임시회 부의 안건 공고</t>
+          <t>포항시 공공하수처리시설 방류수 수질결과 공개(2026.2.28기준)</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>경상도_경산시</t>
+          <t>전라도_화순군</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
+          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
-      </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G213" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9327,18 +9478,26 @@
       </c>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>제279회 화순군의회 임시회 부의 안건 공고</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>경상도_성주군</t>
+          <t>경상도_경산시</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=5</t>
+          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -9367,7 +9526,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=5</t>
+          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=5</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -9391,121 +9550,81 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>전라도_무주군</t>
+          <t>경상도_성주군</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
+          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=5</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>2</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>2026년 무주군 보육정책위원회 심의결과 공고</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>경상도_봉화군</t>
+          <t>경상도_영양군</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=5</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>2</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>2026년 봉화군가족센터 가사돌봄관리사 채용 공고(2차)</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>경상도_봉화군</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
+          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9522,34 +9641,42 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>「포항시 투자유치 종합계획 수립 연구용역」제안서 평가위원(후보자) 모집 공고</t>
+          <t>2026년 봉화군가족센터 가사돌봄관리사 채용 공고(2차)</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>경상도_영양군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=5</t>
+          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
-      </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G219" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9557,8 +9684,16 @@
       </c>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>「포항시 투자유치 종합계획 수립 연구용역」제안서 평가위원(후보자) 모집 공고</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9621,23 +9756,23 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>경상도_구미시</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -9654,42 +9789,34 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>「구미시 공공하수처리시설 수질TMS 유지관리 용역」제안서 평가위원(후보자) 모집 공고</t>
+          <t>2025년 하반기 행정안전부 기구정원 관리실태 감사 결...</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=5</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>6</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9697,36 +9824,36 @@
       </c>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>2025년 하반기 행정안전부 기구정원 관리실태 감사 결...</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>경상도_청도군</t>
+          <t>경상도_구미시</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
+          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D224" t="n">
-        <v>0</v>
-      </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9734,36 +9861,36 @@
       </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>「구미시 공공하수처리시설 수질TMS 유지관리 용역」제안서 평가위원(후보자) 모집 공고</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>경상도_산청군</t>
+          <t>경상도_청도군</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
+          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>10</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9771,36 +9898,36 @@
       </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>2026년 산청군 맞춤형 진로진학 프로그램 제안서 평가(정성) 결과 공고</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>경상도_산청군</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=5</t>
+          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
-      </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9808,73 +9935,77 @@
       </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>2026년 산청군 맞춤형 진로진학 프로그램 제안서 평가(정성) 결과 공고</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>경상도_합천군</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=3</t>
+          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>3</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
+          <t>실패(테이블 없음: table[align='center'][)</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>테이블 없음: table[align='center'][border='0'][cellpadding='0'][cellspacing='1'][width='98%']</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>2026년 소상공인 고효율기기 지원사업 공고</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=5</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=3</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D228" t="n">
-        <v>0</v>
-      </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9882,18 +10013,26 @@
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>2026년 소상공인 고효율기기 지원사업 공고</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>경상도_합천군</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/notice/?p=5</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -9906,14 +10045,10 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table[align='center'][)</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>테이블 없음: table[align='center'][border='0'][cellpadding='0'][cellspacing='1'][width='98%']</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>

--- a/df_log_20260308.xlsx
+++ b/df_log_20260308.xlsx
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경북도로관리사업소</t>
+          <t>강원도로관리사업소</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
+          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -534,12 +534,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>충북도로관리사업소</t>
+          <t>경북도로관리사업소</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -563,12 +563,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>강원도로관리사업소</t>
+          <t>경북도로관리사업소</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -592,12 +592,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>경북도로관리사업소</t>
+          <t>충북도로관리사업소</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6786&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=10&amp;</t>
+          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -711,28 +711,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>인천광역시종합건설본부</t>
+          <t>전남도로관리사업소</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
+          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2016-08-12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -744,40 +744,40 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>공지2026년 신기술특허공법 선정위원회 평가결과 공개</t>
+          <t>장흥 삼수교 개축공사 등 2건 특정공법심의위원회 개최 결과 안내</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2024-07-08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>전남도로관리사업소</t>
+          <t>경남도로관리사업소</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
+          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2016-08-12</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -789,12 +789,12 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>장흥 삼수교 개축공사 등 2건 특정공법심의위원회 개최 결과 안내</t>
+          <t>교량 인상공법 공법제안서 제출안내 공고(국도24호선 남강교 내진..</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2026-02-05</t>
         </is>
       </c>
     </row>
@@ -846,28 +846,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>인천시설관리공단</t>
+          <t>인천광역시종합건설본부</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
+          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,40 +879,40 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[공지]신기술·특허 공법선정위원(후보자) 모집 공고(2026년 청라도시기반사업단 지하차도 및 교량 보수공사)</t>
+          <t>공지2026년 신기술특허공법 선정위원회 평가결과 공개</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>부산시설관리공단</t>
+          <t>인천시설관리공단</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
+          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -924,12 +924,12 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>부산시민공원 잔디밭 도서관 실행 용역 제안서 평가위원 후보자 공개모집 공고</t>
+          <t>[공지]신기술·특허 공법선정위원(후보자) 모집 공고(2026년 청라도시기반사업단 지하차도 및 교량 보수공사)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>전남고시공고</t>
+          <t>경기도_고양시</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
+          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026년 국고보조사업 장애인 집합정보화 교육기관 선정결과 공고2026-03-06</t>
+          <t>『2026년 고양IR데이 운영 용역』 제안서 평가위원(후보자)모집 공고</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1026,23 +1026,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대전시설관리공단</t>
+          <t>경남고시공고</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
+          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1059,7 +1059,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>�ѹ繮ȭü������ 2026�� 3�� ������Ŭ���� �ȳ�</t>
+          <t>2026년 금원산산림자원관리소 숲해설 운영사업 제안서 평가결과 공개</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1071,28 +1071,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>전북도로관리사업소</t>
+          <t>대구시설관리공단</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://www.dpfc.or.kr/sub.php?page_mode=board&amp;Page1=6&amp;Page2=5&amp;Page3=1&amp;Page4=0&amp;sub_mode=p</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1104,40 +1104,40 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>복흥119지역대 신축 건축공사</t>
+          <t>2026�� �뱸�����ü��������� ȯ�� �ü���� �Ⱓ���ٷ��� ����ä�� �����հݿ����� ��ǥ �� ä���ĺ�</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>경남도로관리사업소</t>
+          <t>부산시설관리공단</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
+          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1149,40 +1149,40 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>교량 인상공법 공법제안서 제출안내 공고(국도24호선 남강교 내진..</t>
+          <t>부산시민공원 잔디밭 도서관 실행 용역 제안서 평가위원 후보자 공개모집 공고</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>경기도_고양시</t>
+          <t>전남고시공고</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
+          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1194,7 +1194,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>『2026년 고양IR데이 운영 용역』 제안서 평가위원(후보자)모집 공고</t>
+          <t>2026년 국고보조사업 장애인 집합정보화 교육기관 선정결과 공고2026-03-06</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>전북고시공고</t>
+          <t>전북도로관리사업소</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1251,28 +1251,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>충북고시공고</t>
+          <t>경북고시공고</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1284,24 +1284,24 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>위임국도19호선 괴산 광덕리 도로확포장공사 신기술·특정공법 선정 안내 공고</t>
+          <t>2026년 「경북 관광페스타 in 서울 행사 대행 용역」 제안서 평가위원회 예비평가 위원 모집 공고</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>경북고시공고</t>
+          <t>전북고시공고</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1329,35 +1329,35 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026년 「경북 관광페스타 in 서울 행사 대행 용역」 제안서 평가위원회 예비평가 위원 모집 공고</t>
+          <t>복흥119지역대 신축 건축공사</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경남고시공고</t>
+          <t>경기도_군포시</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
+          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>90</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1374,12 +1374,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026년 금원산산림자원관리소 숲해설 운영사업 제안서 평가결과 공개</t>
+          <t>2026년 주민참여예산 제안사업 공모 공고</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
@@ -1431,76 +1431,76 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경기도_군포시</t>
+          <t>경기도_양주시</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
+          <t>https://www.yangju.go.kr/www/selectBbsNttList.do?bbsNo=13&amp;key=202</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026년 주민참여예산 제안사업 공모 공고</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경기도_양주시</t>
+          <t>충북고시공고</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.yangju.go.kr/www/selectBbsNttList.do?bbsNo=13&amp;key=202</t>
+          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>스킵(IP차단된듯)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>위임국도19호선 괴산 광덕리 도로확포장공사 신기술·특정공법 선정 안내 공고</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1595,28 +1595,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>울산광역시고시공고</t>
+          <t>경기도_오산시</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=5</t>
+          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1628,12 +1628,12 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>수의계약 견적제출 공고 - 2026년 공공하수처리시설 보수공사 실시설계용역</t>
+          <t>2026년 다문화가족 자녀 방문학습지 대상자 모집 공고</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
@@ -1685,28 +1685,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>경기도_오산시</t>
+          <t>울산광역시고시공고</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
+          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=5</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1718,35 +1718,35 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026년 다문화가족 자녀 방문학습지 대상자 모집 공고</t>
+          <t>수의계약 견적제출 공고 - 2026년 공공하수처리시설 보수공사 실시설계용역</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>부산광역시고시공고</t>
+          <t>경기도_동두천시</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.busan.go.kr/nbgosi?curPage=5</t>
+          <t>https://www.ddc.go.kr/ddc/selectGosiList.do?key=340&amp;not_ancmt_se_code=04&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1763,7 +1763,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>「부산광역시 외국인주민정책 기본계획 수립 연구 용역」 제안서 기술능력(정성) 평가결과 공고</t>
+          <t>가축(육용종계 및 육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1775,23 +1775,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>경기도_동두천시</t>
+          <t>부산광역시고시공고</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.ddc.go.kr/ddc/selectGosiList.do?key=340&amp;not_ancmt_se_code=04&amp;pageIndex=2</t>
+          <t>https://www.busan.go.kr/nbgosi?curPage=5</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1808,7 +1808,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>가축(육용종계 및 육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
+          <t>「부산광역시 외국인주민정책 기본계획 수립 연구 용역」 제안서 기술능력(정성) 평가결과 공고</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -1820,23 +1820,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>충남도로관리사업소</t>
+          <t>경기도_연천군</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
+          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>50</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1853,35 +1853,35 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>수의견적 제출 안내 공고(2026년 [논산]국지도68호 강경천교 보수보강공사)</t>
+          <t>연천 전곡리 유적 세계유산 잠정목록 등재를 위한 연구 용역 제안서 평가 결과 공개</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>경기도_연천군</t>
+          <t>강원도_삼척시</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
+          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1898,7 +1898,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>연천 전곡리 유적 세계유산 잠정목록 등재를 위한 연구 용역 제안서 평가 결과 공개</t>
+          <t>고등 졸업학력 검정고시반 강사 모집 공고</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1910,16 +1910,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>경기도_하남시</t>
+          <t>충남도로관리사업소</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.hanam.go.kr/www/selectGosiList.do?key=171&amp;not_ancmt_se_code=01,04&amp;pageIndex=2</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D36" t="n">
         <v>3</v>
@@ -1943,28 +1943,28 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026년 1월 정기분 등록면허세 반송분 공시송달</t>
+          <t>수의견적 제출 안내 공고(2026년 [논산]국지도68호 강경천교 보수보강공사)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>충남고시공고</t>
+          <t>경기도_하남시</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
+          <t>https://www.hanam.go.kr/www/selectGosiList.do?key=171&amp;not_ancmt_se_code=01,04&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
@@ -1988,7 +1988,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>「공인중개사 연수교육 영상 콘텐츠 제작 용역」 제안서 평가위원(후보자) 모집 공고</t>
+          <t>2026년 1월 정기분 등록면허세 반송분 공시송달</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2000,16 +2000,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>경기도_안산시</t>
+          <t>강원도_태백시</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
+          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D38" t="n">
         <v>3</v>
@@ -2033,7 +2033,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>신규주민등록증 통지서 반송자 공고(2009년 2월생)</t>
+          <t>태백시 메이커AI 교육센터 운영 용역 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2045,23 +2045,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경기도_수원시</t>
+          <t>경기도_양평군</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=5</t>
+          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2078,7 +2078,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>민간임대주택에 관한 특별법 위반 과태료 체납 독촉 반송에 따른 공시송달 공고</t>
+          <t>2026년 양평군 조직진단 연구용역 제안서 평가위원회 평가결과 공고</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2090,16 +2090,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>경기도_양평군</t>
+          <t>충남고시공고</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
@@ -2123,7 +2123,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026년 양평군 조직진단 연구용역 제안서 평가위원회 평가결과 공고</t>
+          <t>「공인중개사 연수교육 영상 콘텐츠 제작 용역」 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2135,12 +2135,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>강원도_삼척시</t>
+          <t>강원도_영월군</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
+          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2168,7 +2168,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>고등 졸업학력 검정고시반 강사 모집 공고</t>
+          <t>「영월군 도로기반 지하시설물 전산화사업(산솔면)」 제안서 평가위원(후보자) 모집공고새글</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2225,28 +2225,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>강원도_원주시</t>
+          <t>경기도_포천시</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
+          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2258,28 +2258,28 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>「2026년 혁신도시 문화행사(버스킹) 운영 대행 용역」기술제안서 평가결과 공개</t>
+          <t>포천시 농업기술센터 공고 제2026-145호포천 고병원성AI 발생(축O종계장) 관련 방역대 내 농가 이동제한 및 소독명령</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>강원도_태백시</t>
+          <t>강원도_원주시</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
+          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D44" t="n">
         <v>3</v>
@@ -2303,35 +2303,35 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>태백시 메이커AI 교육센터 운영 용역 제안서 평가위원(후보자) 모집 공고</t>
+          <t>「2026년 혁신도시 문화행사(버스킹) 운영 대행 용역」기술제안서 평가결과 공개</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>강원도_인제군</t>
+          <t>경기도_수원시</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
+          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=5</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2348,28 +2348,28 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026년 제1차 경관위원회 심의결과 공고</t>
+          <t>민간임대주택에 관한 특별법 위반 과태료 체납 독촉 반송에 따른 공시송달 공고</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>강원도_영월군</t>
+          <t>강원도_평창군</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
+          <t>https://www.pc.go.kr/portal/government/government-notification</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D46" t="n">
         <v>3</v>
@@ -2393,7 +2393,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>「영월군 도로기반 지하시설물 전산화사업(산솔면)」 제안서 평가위원(후보자) 모집공고새글</t>
+          <t>「2026년 평창군 자기주도학습 지원 사업 운영 용역」제안서 정성적 평가 결과 공고</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2405,12 +2405,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>강원도_철원군</t>
+          <t>강원도_인제군</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.cwg.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=1226&amp;pageIndex=2</t>
+          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2438,35 +2438,35 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026년 산림교육(숲해설·유아숲교육) 운영 용역 제안서 평가위원회 평가 결과 공개새글</t>
+          <t>2026년 제1차 경관위원회 심의결과 공고</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>충청도_충주시</t>
+          <t>강원도_철원군</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
+          <t>https://www.cwg.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=1226&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2483,7 +2483,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>단월 재해위험개선지구 정비사업 특정공법 선정 기술제안서 제출안내 재공고</t>
+          <t>2026년 산림교육(숲해설·유아숲교육) 운영 용역 제안서 평가위원회 평가 결과 공개새글</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2495,23 +2495,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>강원도_평창군</t>
+          <t>경기도_과천시</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.pc.go.kr/portal/government/government-notification</t>
+          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2528,7 +2528,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>「2026년 평창군 자기주도학습 지원 사업 운영 용역」제안서 정성적 평가 결과 공고</t>
+          <t>도시계획시설(체육시설:승마경기장)사업 실시계획인가 전 열람 · 공고</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2540,23 +2540,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>경기도_과천시</t>
+          <t>충청도_충주시</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2573,7 +2573,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>도시계획시설(체육시설:승마경기장)사업 실시계획인가 전 열람 · 공고</t>
+          <t>단월 재해위험개선지구 정비사업 특정공법 선정 기술제안서 제출안내 재공고</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2585,28 +2585,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기도_시흥시</t>
+          <t>경기도_가평군</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
+          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
         <v>3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2618,28 +2618,28 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>가축 등에 대한 일시 이동중지 명령</t>
+          <t>제20회 경기도장애인생활체육대회 및 제37회 경기도생활체육대축전 개・폐회식 연출대행 용역 제안서 평가위원(후보자) 모집 변경 공고</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경기도_가평군</t>
+          <t>경기도_여주시</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=5</t>
+          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D52" t="n">
         <v>3</v>
@@ -2663,7 +2663,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>제20회 경기도장애인생활체육대회 및 제37회 경기도생활체육대축전 개・폐회식 연출대행 용역 제안서 평가위원(후보자) 모집 변경 공고</t>
+          <t>2026년 마을공동체 주민제안 공모사업 선정...</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -2675,23 +2675,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>강원도_횡성군</t>
+          <t>충청도_계룡시</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
+          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>20</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2708,7 +2708,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>154kV 북원주-횡성 기설송전선로 권원확보사업[4차] 전원개발사업 실시계획 변경승인 및 사업인정에 관한 주민 등의 의견청취 공고</t>
+          <t>2026년도 농작업 보호장비 지원사업 알림</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -2720,16 +2720,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>경기도_여주시</t>
+          <t>충청도_제천시</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=3</t>
+          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D54" t="n">
         <v>3</v>
@@ -2753,35 +2753,35 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026년 마을공동체 주민제안 공모사업 선정...</t>
+          <t>장선천 하천기본계획(재수립)을 위한 전략환경영향평가 항목 등의 결정내용 공고새글</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>충청도_제천시</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2798,7 +2798,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>장선천 하천기본계획(재수립)을 위한 전략환경영향평가 항목 등의 결정내용 공고새글</t>
+          <t>소규모 위험시설 지정 고시(주미동 소교량 외 28건)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -2855,65 +2855,73 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>대구시설관리공단</t>
+          <t>강원도_횡성군</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.dpfc.or.kr/sub.php?page_mode=board&amp;Page1=6&amp;Page2=5&amp;Page3=1&amp;Page4=0&amp;sub_mode=p</t>
+          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>154kV 북원주-횡성 기설송전선로 권원확보사업[4차] 전원개발사업 실시계획 변경승인 및 사업인정에 관한 주민 등의 의견청취 공고</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>경기도_시흥시</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
+          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2925,109 +2933,109 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>소규모 위험시설 지정 고시(주미동 소교량 외 28건)</t>
+          <t>가축 등에 대한 일시 이동중지 명령</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>충청도_계룡시</t>
+          <t>전라도_남원시</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://gyeryong.go.kr/kr/html/sub03/030102.html?GotoPage=2</t>
+          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026년도 농작업 보호장비 지원사업 알림</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>전라도_남원시</t>
+          <t>충청도_보령시</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
+          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>가축(육용종계, 육계) 등에 대한 일시이동중지(Standstill) 명령 알림(경기 포천 HPAI)</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>충청도_예산군</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3044,7 +3052,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>구)충남방적부지개발사업 기본구상 및 타당성조사용역 제안서 평가결과</t>
+          <t>공주시 충남형 농촌리브투게더 신풍지구 임대주택 입주자 추가 모집 공고(8차)</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3056,28 +3064,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>충청도_예산군</t>
+          <t>전라도_김제시</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
+          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3089,40 +3097,40 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026년 봉수산 자연휴양림 데크보행로 교체사업 실시설계용역 수의(2인 이상) 견적제출 안내공고</t>
+          <t>자동차 편취말소 예고 통지에 따른 고시공고</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>전라도_부안군</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
+          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3134,7 +3142,7 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>공주시 충남형 농촌리브투게더 신풍지구 임대주택 입주자 추가 모집 공고(8차)</t>
+          <t>도로기반 지하시설물 전산화 확산사업 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3146,28 +3154,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>충청도_부여군</t>
+          <t>충청도_예산군</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3179,40 +3187,40 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>「부여군 매장문화재 유존지역 정보고도화 사업 지도 제작 및 DB 구축 용역」 제안서 평가위원(후보자) 모집 공고</t>
+          <t>구)충남방적부지개발사업 기본구상 및 타당성조사용역 제안서 평가결과</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>충청도_보령시</t>
+          <t>충청도_예산군</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>20</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3224,40 +3232,40 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>가축(육용종계, 육계) 등에 대한 일시이동중지(Standstill) 명령 알림(경기 포천 HPAI)</t>
+          <t>2026년 봉수산 자연휴양림 데크보행로 교체사업 실시설계용역 수의(2인 이상) 견적제출 안내공고</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>강원도_홍천군</t>
+          <t>충청도_부여군</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278&amp;pageIndex=2</t>
+          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3269,12 +3277,12 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>지적측량기준점(도근점) 성과 고시</t>
+          <t>「부여군 매장문화재 유존지역 정보고도화 사업 지도 제작 및 DB 구축 용역」 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2024-04-17</t>
         </is>
       </c>
     </row>
@@ -3326,28 +3334,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>전라도_부안군</t>
+          <t>충청도_금산군</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
+          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>20계속</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3359,35 +3367,35 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>도로기반 지하시설물 전산화 확산사업 제안서 평가위원(후보자) 모집 공고</t>
+          <t>[일반공고]2026년 금산군 군민리포터 모집 공고</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20계속</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>전라도_곡성군</t>
+          <t>전라도_무안군</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
+          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3404,7 +3412,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>도로명주소 고시(2026-03-06)</t>
+          <t>2026 신도시주민 농업.농촌 체험 활동 추가 모집공고</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3416,28 +3424,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>충청도_금산군</t>
+          <t>충청도_청주시</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
+          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20계속</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3449,40 +3457,40 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[일반공고]2026년 금산군 군민리포터 모집 공고</t>
+          <t>통장 선정 주민투표 공고(28통)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20계속</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>전라도_김제시</t>
+          <t>충청도_음성군</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D71" t="n">
         <v>3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3494,12 +3502,12 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>자동차 편취말소 예고 통지에 따른 고시공고</t>
+          <t>음성 그린에너지 스마트농업타운 투자선도지구 출자타당성 검토 용역 제안서 ...</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -3551,16 +3559,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>전라도_무안군</t>
+          <t>전라도_고창군</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
+          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D73" t="n">
         <v>3</v>
@@ -3584,7 +3592,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026 신도시주민 농업.농촌 체험 활동 추가 모집공고</t>
+          <t>[43425]「고창갯벌 세계유산 OUV 공감 콘텐츠 용역」 제안서 평가 결과 공고첨부파일 있음</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -3596,77 +3604,73 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>경기도_포천시</t>
+          <t>전라도_곡성군</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
+          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>포천시 농업기술센터 공고 제2026-145호포천 고병원성AI 발생(축O종계장) 관련 방역대 내 농가 이동제한 및 소독명령</t>
+          <t>도로명주소 고시(2026-03-06)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>충청도_청주시</t>
+          <t>전라도_영광군</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=5</t>
+          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3678,12 +3682,12 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>통장 선정 주민투표 공고(28통)</t>
+          <t>영광읍 농촌중심지활성화사업 기본계획 승인 고시</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -3735,28 +3739,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>충청도_음성군</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
+          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3768,28 +3772,28 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>음성 그린에너지 스마트농업타운 투자선도지구 출자타당성 검토 용역 제안서 ...</t>
+          <t>제9회 전국동시지방선거 공정선거지원단(선거) 모집 안내</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>전라도_고창군</t>
+          <t>전라도_완도군</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
+          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D78" t="n">
         <v>3</v>
@@ -3813,7 +3817,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[43425]「고창갯벌 세계유산 OUV 공감 콘텐츠 용역」 제안서 평가 결과 공고첨부파일 있음</t>
+          <t>2026년 보길면 윤선도원림 경관조성 및 관리 기간제근로자 최종합격자 공...새로운글</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -3825,16 +3829,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>전라도_완도군</t>
+          <t>경기도_안산시</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.wando.go.kr/wando/sub.cs?m=318&amp;pageIndex=1</t>
+          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D79" t="n">
         <v>3</v>
@@ -3858,7 +3862,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026년 보길면 윤선도원림 경관조성 및 관리 기간제근로자 최종합격자 공...새로운글</t>
+          <t>신규주민등록증 통지서 반송자 공고(2009년 2월생)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -3870,28 +3874,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>전라도_해남군</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
+          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3903,40 +3907,36 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>제9회 전국동시지방선거 공정선거지원단(선거) 모집 안내</t>
+          <t>2026년 전남형 동행 일자리사업 사업제안서(수행기관) 공모...파일</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>전라도_순천시</t>
+          <t>전라도_신안군</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=4</t>
+          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3948,24 +3948,24 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026년 순천만국가정원 관객참여형 디지털인형극 운영 용역 제안서 평가 ...</t>
+          <t>2026년 교통지원과 보조항로팀 기간제근로자 재공고</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2095</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>전라도_영광군</t>
+          <t>전라도_장성군</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
+          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -3993,35 +3993,35 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>영광읍 농촌중심지활성화사업 기본계획 승인 고시</t>
+          <t>2026년 제2회 장성군 건축위원회(건축물해체분야) 심의결...</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>전라도_해남군</t>
+          <t>대구광역시고시공고</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.haenam.go.kr/planweb/board/list.9is?contentUid=18e3368f5d745106015de961fbbd205e&amp;boardUid=18e3368f644b01470164eeb23d7b30f5&amp;contentUid=18e3368f5d745106015de961fbbd205e&amp;recordCountPerPage=100</t>
+          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D83" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4038,40 +4038,40 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026년 전남형 동행 일자리사업 사업제안서(수행기관) 공모...파일</t>
+          <t>「2026년 대구광역시 항공사진 촬영 용역」 제안서 평가위원회 평가위원(후보자) 모집 공고문</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>전라도_장성군</t>
+          <t>경상도_문경시</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
+          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D84" t="n">
         <v>3</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4083,81 +4083,69 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026년 제2회 장성군 건축위원회(건축물해체분야) 심의결...</t>
+          <t>「문경시 문화예술회관 안전난간 설치사업」신기술・특허공법 선정 기술제안서 제출기한 연장 안내 공고</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경상도_상주시</t>
+          <t>경상도_울진군</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.sangju.go.kr/dong/page/15910/11235.tc</t>
+          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP 차단)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>찾아가는 장난감도서관 「누리빵빵」 시범운영 정차지 변경사항 안내</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>전라도_신안군</t>
+          <t>경상도_상주시</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
+          <t>https://www.sangju.go.kr/dong/page/15910/11235.tc</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>15</v>
       </c>
       <c r="D86" t="n">
-        <v>11</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4169,12 +4157,12 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026년 교통지원과 보조항로팀 기간제근로자 재공고</t>
+          <t>찾아가는 장난감도서관 「누리빵빵」 시범운영 정차지 변경사항 안내</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -4226,23 +4214,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>대구광역시고시공고</t>
+          <t>경상도_군위군</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
+          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4259,73 +4247,85 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>「2026년 대구광역시 항공사진 촬영 용역」 제안서 평가위원회 평가위원(후보자) 모집 공고문</t>
+          <t>도로명주소 고시</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경상도_영주시</t>
+          <t>경상도_창원시_의창구</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>[의창구 팔룡동] 여성민방위 기동대 민방위 비상급수 시설 점검</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>충청도_홍성군</t>
+          <t>경상도_창원시_성산구</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4337,40 +4337,40 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>전문건설업 등록(신규, 업종추가) 공고</t>
+          <t>성산구,「2026년 재가의료급여 사업」업무 협약체결</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경상도_군위군</t>
+          <t>경상도_창원시_마산합포구</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>10</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4382,86 +4382,114 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>도로명주소 고시</t>
+          <t>마산합포구, 체납차량 번호판 집중 영치기간 운영새 글</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>전라도_보성군</t>
+          <t>경상도_창원시_마산회원구</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>(마산회원구 가정복지과) 한눈에, 한 손에, 한부모가족 복지안내서 제작·배부새 글</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>경상도_울진군</t>
+          <t>경상도_창원시_진해구</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>스킵(IP 차단)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>(진해구 태백동) 우리동네 한바퀴 지킴이단 순찰활동 실시새 글</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>충청도_서산시</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4489,24 +4517,24 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>「서산시 2차 스마트도시계획 수립 용역」의 제안서 평가위원회 결과 공고</t>
+          <t>2026년 창원시 기후대기 개선사업 한눈에 보기새 글</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>전라도_광양시</t>
+          <t>충청도_홍성군</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
+          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -4534,7 +4562,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026년 숲생태관리인(숲해설가) 채용 공고</t>
+          <t>전문건설업 등록(신규, 업종추가) 공고</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -4546,16 +4574,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>전라도_영암군</t>
+          <t>충청도_서산시</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
+          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D96" t="n">
         <v>3</v>
@@ -4579,73 +4607,85 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>도로명주소 부여 고시</t>
+          <t>「서산시 2차 스마트도시계획 수립 용역」의 제안서 평가위원회 결과 공고</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경상도_김천시</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
+          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>정수장 일일수질검사 결과 안내(2026.3.6.)</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>경상도_창원시_의창구</t>
+          <t>전라도_광양시</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
+          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4657,37 +4697,33 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[의창구 팔룡동] 여성민방위 기동대 민방위 비상급수 시설 점검</t>
+          <t>2026년 숲생태관리인(숲해설가) 채용 공고</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10429/10430.web?gcode=1009&amp;cpage=2</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=2</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>20</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -4702,7 +4738,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026년 창원시 기후대기 개선사업 한눈에 보기새 글</t>
+          <t>[종합소식]양육비 선지급제 안내새 글</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4714,28 +4750,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경상도_창원시_성산구</t>
+          <t>경상도_사천시</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
+          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D100" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4747,40 +4783,40 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>성산구,「2026년 재가의료급여 사업」업무 협약체결</t>
+          <t>[사천시 공고 제2026-449호]담배소매인(사망자)직권취소 및 지정신청 공고새 글</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산합포구</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
+          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4792,73 +4828,85 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>마산합포구, 체납차량 번호판 집중 영치기간 운영새 글</t>
+          <t>2025년 성과관리 평가결과 공개</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=5</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>『덕동생활폐기물매립장 2단계 조성사업』공법선정을 위한 공법선정위원회 평가위원(후보자) 모집 공고</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산회원구</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4870,7 +4918,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>(마산회원구 가정복지과) 한눈에, 한 손에, 한부모가족 복지안내서 제작·배부새 글</t>
+          <t>「주촌면 농촌중심지 활성화사업 기본계획수립 용역」제안서 평가결과 공고</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -4882,28 +4930,28 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>경상도_창원시_진해구</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11101/12355/12400.web</t>
+          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D104" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20새글</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4915,24 +4963,24 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>(진해구 태백동) 우리동네 한바퀴 지킴이단 순찰활동 실시새 글</t>
+          <t>[일자리ㆍ기업]「2026년 소상공인 온라인 입점 지원사업」  참여 소상공인 모집 공고 안내새글</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20새글</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>경상도_남해군_상주면</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%83%81%EC%A3%BC%EB%A9%B4&amp;pageCd=WW0512040402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -4945,14 +4993,10 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>스킵(IP 차단)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -4960,23 +5004,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_거제시</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=5</t>
+          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4993,35 +5037,35 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>『덕동생활폐기물매립장 2단계 조성사업』공법선정을 위한 공법선정위원회 평가위원(후보자) 모집 공고</t>
+          <t>「거제식물원 열린관광 콘텐츠 기획 및 구축 용역」 제안서 평가결과 공고</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>경상도_거제시</t>
+          <t>경상도_의령군</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
+          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5038,33 +5082,37 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>「거제식물원 열린관광 콘텐츠 기획 및 구축 용역」 제안서 평가결과 공고</t>
+          <t>전문건설업 신규등록 공고</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>전라도_순천시</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=2</t>
+          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=4</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
-      </c>
-      <c r="E108" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -5079,7 +5127,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[종합소식]양육비 선지급제 안내새 글</t>
+          <t>2026년 순천만국가정원 관객참여형 디지털인형극 운영 용역 제안서 평가 ...</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -5091,28 +5139,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>경상도_통영시</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
+          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D109" t="n">
         <v>3</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5124,28 +5172,28 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>「주촌면 농촌중심지 활성화사업 기본계획수립 용역」제안서 평가결과 공고</t>
+          <t>통영 수산업・어촌 발전 기본계획 수립 연구용역 제안서 평가위원회 결과 공고</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>경상도_사천시</t>
+          <t>전라도_영암군</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
+          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D110" t="n">
         <v>3</v>
@@ -5169,7 +5217,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[사천시 공고 제2026-449호]담배소매인(사망자)직권취소 및 지정신청 공고새 글</t>
+          <t>도로명주소 부여 고시</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5181,45 +5229,57 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>경상도_함안군</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
+          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026년 함안문화예술회관 「유아 문화예술교육 지원사업」 문화예술교육단체 모집 공고</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>경상도_남해군_서면</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -5232,14 +5292,10 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>스킵(IP 차단)</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -5247,23 +5303,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>경상도_하동군</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
+          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5280,7 +5336,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2025년 성과관리 평가결과 공개</t>
+          <t>경기도 포천시 AI발생 관련 가축(육용종계,육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -5292,28 +5348,28 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_남해군_설천면</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=2</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>20새글</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5325,12 +5381,12 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[일자리ㆍ기업]「2026년 소상공인 온라인 입점 지원사업」  참여 소상공인 모집 공고 안내새글</t>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(설천면)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>20새글</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
@@ -5382,41 +5438,57 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>경상도_남해군_상주면</t>
+          <t>경상도_남해군_미조면</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%83%81%EC%A3%BC%EB%A9%B4&amp;pageCd=WW0512040402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>스킵(IP 차단)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2026년 미조면 취약해안폐기물 대응사업 채용공고</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>경상도_남해군_이동면</t>
+          <t>경상도_남해군_삼동면</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5432,7 +5504,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5444,40 +5516,40 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(이동면)</t>
+          <t>2026년 삼동다락생활문화센터 프로그램 수강생 모집 공고(수정)</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>경상도_의령군</t>
+          <t>경상도_남해군_이동면</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>10</v>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5489,24 +5561,24 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>전문건설업 신규등록 공고</t>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(이동면)</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>경상도_남해군_삼동면</t>
+          <t>경상도_남해군_남면</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -5517,12 +5589,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5534,73 +5606,85 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026년 삼동다락생활문화센터 프로그램 수강생 모집 공고(수정)</t>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(남면)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>경상도_남해군_고현면</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/contents.do?mId=0301040000</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EA%B3%A0%ED%98%84%EB%A9%B4&amp;pageCd=WW0512090402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>제3기 고현면 주민자치회 위원 명단 공개</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>경상도_남해군_미조면</t>
+          <t>경상도_남해군_창선면</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>10</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5612,282 +5696,254 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2026년 미조면 취약해안폐기물 대응사업 채용공고</t>
+          <t>2026년 창선면 해양쓰레기 정화사업(구 바다환경지킴이)기간제근로자 채용 안내</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/contents.do?mId=0301040000</t>
+          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>밀양시 2030's 미래농업 프로젝트 추진계획 용역 제안서 평...</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>경상도_남해군_서면</t>
+          <t>경상도_거창군</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
+          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>스킵(IP 차단)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>제292회 거창군의회 임시회 집회 공고</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>경상도_남해군_남면</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
+          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D124" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>실패(타임아웃)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>타임아웃</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(남면)</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>경상도_함안군</t>
+          <t>서울특별시건설신기술공법선정위원회</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
+          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>2026년 함안문화예술회관 「유아 문화예술교육 지원사업」 문화예술교육단체 모집 공고</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>경상도_남해군_고현면</t>
+          <t>광주도시관리공사</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EA%B3%A0%ED%98%84%EB%A9%B4&amp;pageCd=WW0512090402&amp;siteGubun=portal</t>
+          <t>https://www.gumc.or.kr/news/bidding</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>9</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>제3기 고현면 주민자치회 위원 명단 공개</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>경상도_통영시</t>
+          <t>광주도시관리공사</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
+          <t>https://www.gumc.or.kr/news/news</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>통영 수산업・어촌 발전 기본계획 수립 연구용역 제안서 평가위원회 결과 공고</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>경상도_남해군_설천면</t>
+          <t>세종소개공고</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
+          <t>https://www.sejong.go.kr/prog/publicNotice/kor/sub02_0303/C1/list.do</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>10</v>
       </c>
       <c r="D128" t="n">
-        <v>10</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5899,40 +5955,36 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(설천면)</t>
+          <t>2026년 제54회 어버이날 공모선정 결과</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>경상도_남해군_창선면</t>
+          <t>경기도감사위원회고시공고</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
+          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
         </is>
       </c>
       <c r="C129" t="n">
+        <v>11</v>
+      </c>
+      <c r="D129" t="n">
         <v>10</v>
       </c>
-      <c r="D129" t="n">
-        <v>9</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5944,28 +5996,28 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
-          <t>2026년 창선면 해양쓰레기 정화사업(구 바다환경지킴이)기간제근로자 채용 안내</t>
+          <t>신기술·특허 공법 선정 안내 정정 공고(묵현천 지방하천 정비사업)</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>경상도_하동군</t>
+          <t>경기도_수원_팔달구</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
+          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D130" t="n">
         <v>3</v>
@@ -5989,7 +6041,7 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>경기도 포천시 AI발생 관련 가축(육용종계,육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
+          <t>장애인전용주차구역 주차위반 압류통지 반송분 공시송달 공고</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -6001,28 +6053,24 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>경상도_거창군</t>
+          <t>경기도_용인시공법선정위원회</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
+          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -6034,24 +6082,24 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
-          <t>제292회 거창군의회 임시회 집회 공고</t>
+          <t>2026년 제2회, 제3회 신기술·특허 공법선정위원회 평가결...</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2084</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>광주광역시고시공고</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=3</t>
+          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -6079,7 +6127,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
-          <t>밀양시 2030's 미래농업 프로젝트 추진계획 용역 제안서 평...</t>
+          <t>신기술·특허공법 제안 재공고[광주도시철도 2호선 2단계 기본 및 실시설계용역(토목/건축 설계2공구)]</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -6091,89 +6139,113 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>경상도_울릉군</t>
+          <t>경기도_수원_장안구</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>불법옥외광고물 자진정비 시정명령 사전안내 반송에 따른 공시송달 공고</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>경상도_안동시</t>
+          <t>경기도_수원_권선구</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>이륜자동차 정기검사 신청기간 경과 알림 및 명령서 반송분 공시송달 공고</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>경상도_경주시</t>
+          <t>경기도_부천시</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423&amp;pageNo=3</t>
+          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6183,18 +6255,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>대곡금척 자연재해위험개선지구 정비사업 실시계획(변경) 공고</t>
+          <t>2026년 마을공동체 활동매니저 합격자 공고</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -6206,30 +6274,38 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>경상도_고성군</t>
+          <t>대전광역시고시공고</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+          <t>실패(타임아웃)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
+          <t>타임아웃</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -6239,30 +6315,38 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경기도_광주시</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
+          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
+          <t>실패(타임아웃)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
+          <t>타임아웃</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -6272,23 +6356,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경기도_성남시수정구</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=763&amp;pageid=2</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6298,161 +6382,173 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>남영덕 하이패스IC(고속국도 65호선) 추가설치 타당성조사 용역 제안서 평가위원(후보자) 모집 공고</t>
+          <t>무단방치차량 강제처리(폐차) 및 이해관계인 권리행사 공고</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>경상도_진주시</t>
+          <t>경기도_안양시</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
+          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>「박달동 및 인덕원동 하수도정비 중점관리지역 도시침수예방사업」공법선정평가위원회 평가위원(후보자) 공개모집 공고</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>경상도_창녕군</t>
+          <t>경기고시공고</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
+          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=5</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>HTTP ?: 새 URL 탐색 실패</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>『3기 신도시 리츠 도입 연구용역 2건』제안서 평가위원 후보자 공개모집</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>경상도_문경시</t>
+          <t>경기도_의왕시</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
+          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D141" t="n">
         <v>3</v>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>「문경시 문화예술회관 안전난간 설치사업」신기술・특허공법 선정 기술제안서 제출기한 연장 안내 공고</t>
+          <t>2026년 의왕어린이철도축제 행사대행용역 제안서 평가결과 공개</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>경기도_성남시중원구</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6462,18 +6558,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>양산 매장유산 유존지역 정보고도화 사업(비도심) 제안서 평가위원(후보자) 공개모집 공고</t>
+          <t>무단방치 이륜차 자진처리명령서 공시송달 및 강제처리(폐차) 공고</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -6485,153 +6577,205 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>경기도_이천시</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
+          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>10</v>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Zero-Selector성공</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>2023년 함평군 지적재조사사업 완료 공람·공고</t>
+          <t>도로명주고 부여 고시</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>광주도시관리공사</t>
+          <t>경기도_성남시분당구</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/bidding</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>소액수의 견적제출 안내 공고-가로수 수형관리공사(판교지구 등)</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>광주도시관리공사</t>
+          <t>경기도_성남시</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/news</t>
+          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>도로명주소(건물번호) 부여 고시</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>서울특별시건설신기술공법선정위원회</t>
+          <t>경기도_의정부시</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://news.seoul.go.kr/citybuild/archives/516614#list/1</t>
+          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>스킵(IP차단된듯)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>도로점용(굴착)허가 내용 공고[제2026-의정부동점용(굴착)-2호, 대○이○에○, 가능동 15-484(가능동 15-79)]</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>세종소개공고</t>
+          <t>강원도_동해시</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.sejong.go.kr/prog/publicNotice/kor/sub02_0303/C1/list.do</t>
+          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D147" t="n">
-        <v>3</v>
-      </c>
-      <c r="E147" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -6646,36 +6790,40 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>가축 등에 대한 일시 이동중지 명령(AI)</t>
+          <t>「동해시 교육발전 중장기 기본계획 수립 연구 용역」 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>경기도감사위원회고시공고</t>
+          <t>경기도_평택시</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://newtech.gg.go.kr/main/pblanNow.do</t>
+          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D148" t="n">
-        <v>10</v>
-      </c>
-      <c r="E148" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6687,35 +6835,35 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>신기술·특허 공법 선정 안내 정정 공고(묵현천 지방하천 정비사업)</t>
+          <t>주민등록 장기 거주불명자 최고 공고</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>경기도_수원_팔달구</t>
+          <t>강원도_양구군</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
+          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D149" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6732,35 +6880,35 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>장애인전용주차구역 주차위반 압류통지 반송분 공시송달 공고</t>
+          <t>[양구군 공고 제2026-228호] 수입천 오지마을 시끌벅적 활성화 사업 건축설계공모(제안공모) 서면질의         ...</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>경기도_수원_권선구</t>
+          <t>강원도_속초시</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
+          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6770,18 +6918,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>이륜자동차 정기검사 신청기간 경과 알림 및 명령서 반송분 공시송달 공고</t>
+          <t>속초 도시계획시설(도로: 중로3-35호선) 실시계획인가(변경) 고시</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -6793,23 +6937,23 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>경기도_수원_장안구</t>
+          <t>강원도_강릉시</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3750000&amp;epcCheck=Y</t>
+          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6819,18 +6963,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>불법옥외광고물 자진정비 시정명령 사전안내 반송에 따른 공시송달 공고</t>
+          <t>2026년도 경포동 환경관리원 대체인력(기간제근로자) 채용 합격자 공고</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -6842,23 +6982,23 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>경기도_수원_영통구</t>
+          <t>강원도_고성군</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
+          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6875,36 +7015,40 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>친환경자동차법 위반 과태료 사전통지 반송분 공시송달 공고</t>
+          <t>고성군 친환경로컬푸드매장 관리위탁 제안서 제출안내 및 입찰공고(재공고)</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>경기도_용인시공법선정위원회</t>
+          <t>경기도_안성시</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.yongin.go.kr/user/bbs/BD_selectBbsList.do?q_bbsCode=1156</t>
+          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
-      </c>
-      <c r="E153" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6916,35 +7060,35 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>2026년 제2회, 제3회 신기술·특허 공법선정위원회 평가결...</t>
+          <t>공도 도시계획시설(공공ㆍ문화체육시설: 문화 및 사회복지시설-공도시민청) 실시계획(변경)작성 고시</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>광주광역시고시공고</t>
+          <t>강원도_화천군</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://sido.gwangju.go.kr/citynet/jsp/sap/SAPGosiBizProcess.do?command=searchList&amp;flag=gosiGL&amp;svp=Y</t>
+          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6961,7 +7105,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
-          <t>신기술·특허공법 제안 재공고[광주도시철도 2호선 2단계 기본 및 실시설계용역(토목/건축 설계2공구)]</t>
+          <t>2026년 실외사육견 중성화 지원 사업시행자(동물병원) 모집 공고</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -6973,23 +7117,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>경기도_광주시</t>
+          <t>경기도_파주시</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
+          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6999,91 +7143,71 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>『2026년 광주시 장애인평생학습센터 강의안 제안』공모</t>
+          <t>파랑해 이벤트 Vol. 1 「내가 그린 파랑, 띠-부 스티커가로 태어나다!」 새학기 맞이 공모이벤트N</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>대전광역시고시공고</t>
+          <t>충청도_청주시_서원구</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단)</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>제안서 평가위원 공개모집 재공고(성북동체육공원 파크골프장 조성 타당성 조사 및 기본계획 수립용역)</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>경기도_성남시수정구</t>
+          <t>충청도_괴산군</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7100,7 +7224,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>무단방치차량 강제처리(폐차) 및 이해관계인 권리행사 공고</t>
+          <t>도로명주소 고시</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -7112,23 +7236,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>경기도_용인시처인구</t>
+          <t>충청도_청주시_흥덕구</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7145,7 +7269,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>무단 방치자전거 보관 및 처분 공고</t>
+          <t>압류자동차 공매 공고</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -7157,23 +7281,23 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>경기고시공고</t>
+          <t>강원도_양양군</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=5</t>
+          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7190,7 +7314,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>『3기 신도시 리츠 도입 연구용역 2건』제안서 평가위원 후보자 공개모집</t>
+          <t>「행정재산 실태조사 및 공유재산 통합 DB구축 용역」 제안서 평가위원회 평가 결과 공고</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -7202,19 +7326,19 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>경기도_부천시</t>
+          <t>충청도_보은군</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
+          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -7223,7 +7347,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7235,35 +7359,35 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>2026년 마을공동체 활동매니저 합격자 공고</t>
+          <t>경기 포천 육용종계농장 고병원성 조류인플루엔자 발생관련 가축(육용종계, 육계) 등에 대한 일시이동중지 명령 알림</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>경기도_성남시</t>
+          <t>충청도_영동군</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7280,7 +7404,7 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>도로명주소(건물번호) 부여 고시</t>
+          <t>금계천 금계지구 지방하천 정비사업 공법선정 심의위원회 평가결과 공고</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -7292,21 +7416,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>경기도_의왕시</t>
+          <t>강원도_정선군</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://eminwon.uiwang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=A&amp;epcCheck=''</t>
+          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D162" t="n">
         <v>3</v>
       </c>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -7321,7 +7449,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>2026년 의왕어린이철도축제 행사대행용역 제안서 평가결과 공개</t>
+          <t>주택건설사업계획 승인 고시 [SG아파트_세기건설(주)]</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -7333,61 +7461,49 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>경기도_안양시</t>
+          <t>충청도_당진시</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
+          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>3</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr"/>
+          <t>실패(타임아웃)</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>타임아웃</t>
+        </is>
+      </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>「박달동 및 인덕원동 하수도정비 중점관리지역 도시침수예방사업」공법선정평가위원회 평가위원(후보자) 공개모집 공고</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>경기도_성남시중원구</t>
+          <t>충청도_증평군</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D164" t="n">
         <v>3</v>
@@ -7411,35 +7527,35 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>무단방치 이륜차 자진처리명령서 공시송달 및 강제처리(폐차) 공고</t>
+          <t>2026년 제1회 증평군 주소정보위원회 심의 결과 공고</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>경기도_이천시</t>
+          <t>충청도_단양군</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
+          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7456,7 +7572,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>도로명주고 부여 고시</t>
+          <t>2026년 지적재조사사업 측량·조사 등의 위탁고시</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -7468,16 +7584,16 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>경기도_성남시분당구</t>
+          <t>강원도_춘천시</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3810000&amp;list_gubun=&amp;nodate_recent_mm=12&amp;not_ancmt_se_code=&amp;recent_mm=3</t>
+          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D166" t="n">
         <v>3</v>
@@ -7501,7 +7617,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>소액수의 견적제출 안내 공고-가로수 수형관리공사(판교지구 등)</t>
+          <t>강촌분구 외 5개소 노후하수관로 정비사업 실시설계용역 사업 집행계획 및 사업수행능력평가서 제출안내 공고</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -7513,28 +7629,28 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>강원도_동해시</t>
+          <t>충청도_진천군</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
+          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D167" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7546,40 +7662,40 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>「동해시 교육발전 중장기 기본계획 수립 연구 용역」 제안서 평가위원(후보자) 모집 공고</t>
+          <t>『구암저수지 둘레길 조성사업』 신기술·특허공법 선정 공법제안서 제출안내 ...</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>경기도_의정부시</t>
+          <t>충청도_서천군</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.ui4u.go.kr/portal/saeol/gosiList.do?seCode=01&amp;mId=0301040000</t>
+          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7591,35 +7707,35 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>도로점용(굴착)허가 내용 공고[제2026-의정부동점용(굴착)-2호, 대○이○에○, 가능동 15-484(가능동 15-79)]</t>
+          <t>도로명주소 고시</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>경기도_평택시</t>
+          <t>충청도_청주시_상당구</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7636,68 +7752,80 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>주민등록 장기 거주불명자 최고 공고</t>
+          <t>학대피해아동쉼터 운영 수탁자 선정 심의결과 공고</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>강원도_고성군</t>
+          <t>충청도_천안시</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
+          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>「풍서천 재해복구사업(개선)」재난안전신기술 공법선정을 위한 기술제안서 제...</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>강원도_강릉시</t>
+          <t>전라도_군산시</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=3</t>
+          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7714,7 +7842,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026년도 경포동 환경관리원 대체인력(기간제근로자) 채용 합격자 공고</t>
+          <t>어린이보호구역 신규지정 고시(내흥초등학교,새빛유치원)</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -7726,56 +7854,68 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>강원도_양구군</t>
+          <t>충청도_논산시</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
+          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>지적기준점(도근점) 성과고시(세계좌표 3점)</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>강원도_속초시</t>
+          <t>충청도_아산시</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
+          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7792,7 +7932,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>속초 도시계획시설(도로: 중로3-35호선) 실시계획인가(변경) 고시</t>
+          <t>2026년 아산 국가유산 야행 행사대행 용역 제안서 평가결과 및 우선협상...</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -7804,23 +7944,23 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>강원도_화천군</t>
+          <t>전라도_순창군</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>http://eminwon.ihc.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04</t>
+          <t>http://eminwon.sunchang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7837,7 +7977,7 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>2026년 실외사육견 중성화 지원 사업시행자(동물병원) 모집 공고</t>
+          <t>북서부재생활성화지역(복흥·쌍치·구림) 기본계획 수립 용역 제안서 평가위원 모집공고</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -7849,28 +7989,28 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>경기도_안성시</t>
+          <t>전라도_장수군</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
+          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D175" t="n">
         <v>3</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7882,40 +8022,40 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>공도 도시계획시설(공공ㆍ문화체육시설: 문화 및 사회복지시설-공도시민청) 실시계획(변경)작성 고시</t>
+          <t>「장수군 이종무 장군 재조명 및 기념사업 지원에 관한 조례안」입법예고</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>충청도_괴산군</t>
+          <t>전라도_무주군</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>10</v>
       </c>
       <c r="D176" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7927,57 +8067,73 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>도로명주소 고시</t>
+          <t>용역[2025년도 수질오염 총량관리 이행평가 용역] 수의견적 공고</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>충청도_청주시_서원구</t>
+          <t>전라도_임실군</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
+          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>스킵(IP차단)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>2026년 임실군 가로수 조성관리계획 고시</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>강원도_양양군</t>
+          <t>전라도_정읍시</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D178" t="n">
         <v>3</v>
@@ -8001,7 +8157,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>「행정재산 실태조사 및 공유재산 통합 DB구축 용역」 제안서 평가위원회 평가 결과 공고</t>
+          <t>칠보면 와우제 보수보강공사 긴급 입찰공고</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -8013,16 +8169,16 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>경기도_파주시</t>
+          <t>전라도_목포시</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
+          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D179" t="n">
         <v>3</v>
@@ -8046,7 +8202,7 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>파랑해 이벤트 Vol. 1 「내가 그린 파랑, 띠-부 스티커가로 태어나다!」 새학기 맞이 공모이벤트N</t>
+          <t>공유수면 점용사용 변경허가 고시새로운글</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -8058,23 +8214,23 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>충청도_청주시_흥덕구</t>
+          <t>전라도_장흥군</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;cha_dep_code_nm=57300220000,57300210000,57300040000,57300230000,57300060000,57300070000,57300240000,57300090000,57102000000&amp;yyyy=2018</t>
+          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8091,35 +8247,35 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>압류자동차 공매 공고</t>
+          <t>「장흥 쓰레기위생매립장 침출수처리시설 개선사업」 침출수처리 공법..</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>강원도_정선군</t>
+          <t>전라도_완주군</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://eminwon.wanju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8129,18 +8285,14 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>주택건설사업계획 승인 고시 [SG아파트_세기건설(주)]</t>
+          <t>2026년 저소득층 그린리모델링 사업 공고</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -8152,73 +8304,62 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>충청도_단양군</t>
+          <t>전라도_담양군</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
+          <t>실패(Alert Text: /eminwon/getSearch)</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Alert Text: /eminwon/getSearchList 페이징 오류
+Message: unexpected alert open: {Alert text : /eminwon/get</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>2026년 지적재조사사업 측량·조사 등의 위탁고시</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>충청도_보은군</t>
+          <t>전라도_고흥군</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
+          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D183" t="n">
         <v>3</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8230,40 +8371,40 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>경기 포천 육용종계농장 고병원성 조류인플루엔자 발생관련 가축(육용종계, 육계) 등에 대한 일시이동중지 명령 알림</t>
+          <t>도로명주소 고시</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>충청도_영동군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.yd21.go.kr/kr/html/sub02/020103.html</t>
+          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D184" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -8275,90 +8416,114 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>금계천 금계지구 지방하천 정비사업 공법선정 심의위원회 평가결과 공고</t>
+          <t>포항시 공공하수처리시설 방류수 수질결과 공개(2026.2.28기준)</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>충청도_증평군</t>
+          <t>전라도_여수시</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
+          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=4</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
-      </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>「2026 유엔기후변화협약 기후주간 행사개최 지원사업」 제안서 평가위원(...새로운글</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>충청도_진천군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
+          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
-      </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>「포항시 투자유치 종합계획 수립 연구용역」제안서 평가위원(후보자) 모집 공고</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>충청도_당진시</t>
+          <t>경상도_청송군</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
+          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -8371,14 +8536,10 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>스킵(fail)</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
@@ -8386,141 +8547,141 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>충청도_서천군</t>
+          <t>경상도_청송군</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>10</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>도로명주소 고시</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>충청도_청양군</t>
+          <t>경상도_구미시</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
+          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
-      </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>「구미시 공공하수처리시설 수질TMS 유지관리 용역」제안서 평가위원(후보자) 모집 공고</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>충청도_태안군</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
-      </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2025년 하반기 행정안전부 기구정원 관리실태 감사 결...</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>강원도_춘천시</t>
+          <t>경상도_청도군</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
+          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>3</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>성공</t>
@@ -8528,59 +8689,63 @@
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>강촌분구 외 5개소 노후하수관로 정비사업 실시설계용역 사업 집행계획 및 사업수행능력평가서 제출안내 공고</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>전라도_전주시</t>
+          <t>경상도_산청군</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
+          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
-      </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>2026년 산청군 맞춤형 진로진학 프로그램 제안서 평가(정성) 결과 공고</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>충청도_천안시</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=3</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -8591,12 +8756,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -8608,7 +8773,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>「풍서천 재해복구사업(개선)」재난안전신기술 공법선정을 위한 기술제안서 제...</t>
+          <t>2026년 소상공인 고효율기기 지원사업 공고</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -8620,23 +8785,23 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>충청도_아산시</t>
+          <t>경상도_함양군</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
+          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8653,7 +8818,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>2026년 아산 국가유산 야행 행사대행 용역 제안서 평가결과 및 우선협상...</t>
+          <t>함양군 공공디자인 진흥계획 수립 용역 제안서 평가위원회 평가결과 공개</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -8665,236 +8830,200 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>전라도_군산시</t>
+          <t>대전시설관리공단</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://eminwon.gunsan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
-      </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table[summary='고시공고 목록)</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>테이블 없음: table[summary='고시공고 목록'] tbody tr[bgcolor]</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>�ѹ繮ȭü������ 2026�� 3�� ������Ŭ���� �ȳ�</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>충청도_청주시_상당구</t>
+          <t>경상도_김천시</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
+          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>3</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr"/>
+          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>HTTP 0: 새 URL 탐색 실패</t>
+        </is>
+      </c>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>학대피해아동쉼터 운영 수탁자 선정 심의결과 공고</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>전라도_익산시</t>
+          <t>경상도_영주시</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
+          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(27) &gt; )</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(27) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>용동면 기초생활거점조성사업(2단계) 기본계획 및 시행계획 승인 고시</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>충청도_논산시</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
+          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>지적기준점(도근점) 성과고시(세계좌표 3점)</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>전라도_순창군</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>http://eminwon.sunchang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05</t>
+          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>3</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>북서부재생활성화지역(복흥·쌍치·구림) 기본계획 수립 용역 제안서 평가위원 모집공고</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>전라도_장수군</t>
+          <t>강원도_홍천군</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://eminwon.jangsu.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,04,05,03&amp;yyyy=2017&amp;subCheck=Y</t>
+          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278</t>
         </is>
       </c>
       <c r="C200" t="n">
         <v>10</v>
       </c>
       <c r="D200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -8903,36 +9032,40 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>「장수군 이종무 장군 재조명 및 기념사업 지원에 관한 조례안」입법예고</t>
+          <t>지적측량기준점(도근점) 성과 고시</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>전라도_진안군</t>
+          <t>전라도_보성군</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -8945,12 +9078,12 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -8960,12 +9093,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>전라도_나주시</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -8978,357 +9111,269 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>전라도_임실군</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>3</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>2026년 임실군 가로수 조성관리계획 고시</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>전라도_정읍시</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>2</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>칠보면 와우제 보수보강공사 긴급 입찰공고</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>전라도_무주군</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
+          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>3</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>2026년 무주군 보육정책위원회 심의결과 공고</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>전라도_목포시</t>
+          <t>경상도_고성군</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
+          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr"/>
+          <t>실패(URL 복구 후에도 접근 불가)</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>URL 복구 후에도 접근 불가</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>공유수면 점용사용 변경허가 고시새로운글</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>전라도_완주군</t>
+          <t>경상도_진주시</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://eminwon.wanju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>4</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr"/>
+          <t>실패(URL 복구 후 파싱 실패: 테이블 없음: div.li)</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>URL 복구 후 파싱 실패: 테이블 없음: div.list1f1t3i1</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>2026년 저소득층 그린리모델링 사업 공고</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>전라도_장흥군</t>
+          <t>경상도_울릉군</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
+          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>4</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>「장흥 쓰레기위생매립장 침출수처리시설 개선사업」 침출수처리 공법..</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>전라도_고흥군</t>
+          <t>경상도_창녕군</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
+          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>3</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr"/>
+          <t>실패(URL 복구 후 파싱 실패: 테이블 없음: div.li)</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>URL 복구 후 파싱 실패: 테이블 없음: div.list1f1t3i1</t>
+        </is>
+      </c>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>도로명주소 고시</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>전라도_여수시</t>
+          <t>경상도_경주시</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=4</t>
+          <t>https://www.gyeongju.go.kr/open_content/ko/page.do?mnu_uid=423</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9338,14 +9383,18 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>「2026 유엔기후변화협약 기후주간 행사개최 지원사업」 제안서 평가위원(...새로운글</t>
+          <t>대곡금척 자연재해위험개선지구 정비사업 실시계획(변경) 공고</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -9357,12 +9406,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>전라도_담양군</t>
+          <t>경상도_안동시</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
+          <t>https://www.andong.go.kr/portal/contents.do?mId=0401020000</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -9373,104 +9422,104 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>전문건설업 자료제출 공문 반송에 따른 공시송달 공고</t>
+          <t>예안면 이장심사위원회 심의 결과 공고</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/board/post/list.do?bcIdx=100&amp;mid=0201010000&amp;token=1749000149392</t>
+          <t>https://www.yd.go.kr/?page_id=763</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D212" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>자가치유성공</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>포항시 공공하수처리시설 방류수 수질결과 공개(2026.2.28기준)</t>
+          <t>남영덕 하이패스IC(고속국도 65호선) 추가설치 타당성조사 용역 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>전라도_화순군</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
+          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>3</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9478,26 +9527,18 @@
       </c>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>제279회 화순군의회 임시회 부의 안건 공고</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>경상도_경산시</t>
+          <t>경기도_수원_영통구</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -9510,10 +9551,14 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr"/>
+          <t>실패(테이블 없음: table.p-table.default )</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>테이블 없음: table.p-table.default tbody</t>
+        </is>
+      </c>
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
@@ -9521,12 +9566,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>경상도_성주군</t>
+          <t>경기도_용인시처인구</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=5</t>
+          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -9539,10 +9584,14 @@
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr"/>
+          <t>실패(테이블 없음: table.boardDefalut tbo)</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>테이블 없음: table.boardDefalut tbody tr</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
@@ -9550,12 +9599,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>경상도_성주군</t>
+          <t>충청도_청양군</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=5</t>
+          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -9568,10 +9617,14 @@
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
@@ -9579,12 +9632,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>경상도_영양군</t>
+          <t>충청도_태안군</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=5</t>
+          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -9597,10 +9650,14 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
@@ -9608,102 +9665,78 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>경상도_봉화군</t>
+          <t>전라도_전주시</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>2</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>2026년 봉화군가족센터 가사돌봄관리사 채용 공고(2차)</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>전라도_진안군</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
+          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>3</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>「포항시 투자유치 종합계획 수립 연구용역」제안서 평가위원(후보자) 모집 공고</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>경상도_청송군</t>
+          <t>전라도_나주시</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
+          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -9716,10 +9749,14 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
@@ -9727,28 +9764,40 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>경상도_청송군</t>
+          <t>전라도_화순군</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
+          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
-      </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
@@ -9756,23 +9805,23 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>전라도_익산시</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
+          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D222" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -9782,31 +9831,27 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(27) &gt; )</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(27) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>2025년 하반기 행정안전부 기구정원 관리실태 감사 결...</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>경상도_예천군</t>
+          <t>경상도_경산시</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=5</t>
+          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -9830,23 +9875,23 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>경상도_구미시</t>
+          <t>경상도_봉화군</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
+          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D224" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -9856,31 +9901,27 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr"/>
+          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+        </is>
+      </c>
       <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>「구미시 공공하수처리시설 수질TMS 유지관리 용역」제안서 평가위원(후보자) 모집 공고</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>경상도_청도군</t>
+          <t>경상도_성주군</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.cheongdo.go.kr/portal/saeol/gosi/list.do?mid=0301020000&amp;token=1703813401840</t>
+          <t>https://www.sj.go.kr/page.do?mnu_uid=1044&amp;pageNo=5</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -9904,30 +9945,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>경상도_산청군</t>
+          <t>경상도_성주군</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
+          <t>https://sj.go.kr/S1012/page.do?mnu_uid=2189&amp;pageNo=5</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>10</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>성공</t>
@@ -9935,26 +9968,18 @@
       </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>2026년 산청군 맞춤형 진로진학 프로그램 제안서 평가(정성) 결과 공고</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>경상도_합천군</t>
+          <t>경상도_영양군</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
+          <t>https://www.yyg.go.kr/www/organization/yyg_news/notification?page=5</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -9967,14 +9992,10 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table[align='center'][)</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>테이블 없음: table[align='center'][border='0'][cellpadding='0'][cellspacing='1'][width='98%']</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
@@ -9982,30 +10003,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>경상도_예천군</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=3</t>
+          <t>https://www.ycg.kr/open.content/ko/administrative/news/announcement/?p=5</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>3</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>성공</t>
@@ -10013,16 +10026,8 @@
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>2026년 소상공인 고효율기기 지원사업 공고</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10056,47 +10061,35 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>경상도_함양군</t>
+          <t>경상도_합천군</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
+          <t>https://eminwon.hc.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>3</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
+          <t>실패(테이블 없음: table[align='center'][)</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>테이블 없음: table[align='center'][border='0'][cellpadding='0'][cellspacing='1'][width='98%']</t>
+        </is>
+      </c>
       <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>함양군 공공디자인 진흥계획 수립 용역 제안서 평가위원회 평가결과 공개</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/df_log_20260308.xlsx
+++ b/df_log_20260308.xlsx
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>강원도로관리사업소</t>
+          <t>충북도로관리사업소</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -505,12 +505,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경북플랫폼</t>
+          <t>경북도로관리사업소</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -563,12 +563,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>경북도로관리사업소</t>
+          <t>경북플랫폼</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/open_contents/section/finace/page.do?mnu_uid=2737&amp;LARGE_CODE=330&amp;MEDIUM_CODE=30&amp;SMALL_CODE=20&amp;SMALL_CODE2=30&amp;mnu_order=4</t>
+          <t>https://www.gb.go.kr/Main/open_contents/section/newtech/page.do?mnu_uid=5890&amp;LARGE_CODE=630&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;&amp;mnu_order=5</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -592,12 +592,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>충북도로관리사업소</t>
+          <t>강원도로관리사업소</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/road/selectBbsNttList.do?key=1975&amp;bbsNo=292&amp;searchCnd=SJ&amp;searchKrwd=</t>
+          <t>https://state.gwd.go.kr/road/announce?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -621,28 +621,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>서울시설관리공단</t>
+          <t>울산시설관리공단</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
+          <t>https://www.uic.or.kr/notify/noti01.do</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -654,40 +654,40 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>탄천1고가교 도장 보수공사 신기술·특허공법(강교도장) 선정 제안서 제출 안내 공고</t>
+          <t>「2026년도 태화강수상스포츠센터 운영 용역」 사업자 선정 제안서 평가위원회 평가위원(후보자) 공개모집 공고</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>울산시설관리공단</t>
+          <t>전남도로관리사업소</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.uic.or.kr/notify/noti01.do</t>
+          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2016-08-12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,40 +699,40 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>「2026년도 태화강수상스포츠센터 운영 용역」 사업자 선정 제안서 평가위원회 평가위원(후보자) 공개모집 공고</t>
+          <t>장흥 삼수교 개축공사 등 2건 특정공법심의위원회 개최 결과 안내</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-07-08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>전남도로관리사업소</t>
+          <t>인천시설관리공단</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://road.jeonnam.go.kr/main/na/ntt/selectNttList.do?mi=9094&amp;bbsId=7</t>
+          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2016-08-12</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -744,35 +744,35 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>장흥 삼수교 개축공사 등 2건 특정공법심의위원회 개최 결과 안내</t>
+          <t>[공지]신기술·특허 공법선정위원(후보자) 모집 공고(2026년 청라도시기반사업단 지하차도 및 교량 보수공사)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>경남도로관리사업소</t>
+          <t>인천광역시종합건설본부</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
+          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -789,35 +789,35 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>교량 인상공법 공법제안서 제출안내 공고(국도24호선 남강교 내진..</t>
+          <t>공지2026년 신기술특허공법 선정위원회 평가결과 공개</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>세종시설관리공단</t>
+          <t>대전시설관리공단</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
+          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025년 행복아파트 하반기 모집 입주자 및 예비입주자 선정결과 공고</t>
+          <t>�ѹ繮ȭü������ 2026�� 3�� ������Ŭ���� �ȳ�</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -846,28 +846,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>인천광역시종합건설본부</t>
+          <t>세종시설관리공단</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.incheon.go.kr/jonggeon/JO020101</t>
+          <t>https://www.sjfmc.or.kr/kor/sub02_01/cop/bbs/BBSMSTR_000000000013/selectBoardList.do</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -879,40 +879,40 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>공지2026년 신기술특허공법 선정위원회 평가결과 공개</t>
+          <t>2025년 행복아파트 하반기 모집 입주자 및 예비입주자 선정결과 공고</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>인천시설관리공단</t>
+          <t>강원고시공고</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.insiseol.or.kr/life/urban/notice/notice.jsp</t>
+          <t>https://state.gwd.go.kr/portal/bulletin/notification?pageIndex=1&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -924,40 +924,40 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[공지]신기술·특허 공법선정위원(후보자) 모집 공고(2026년 청라도시기반사업단 지하차도 및 교량 보수공사)</t>
+          <t>2026년 제1회 강원특별자치도 건축물미술작품 심의위원회 심의결과 공고</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강원고시공고</t>
+          <t>대구시설관리공단</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://state.gwd.go.kr/portal/bulletin/notification?pageIndex=1&amp;recordCountPerPage=90</t>
+          <t>https://www.dpfc.or.kr/sub.php?page_mode=board&amp;Page1=6&amp;Page2=5&amp;Page3=1&amp;Page4=0&amp;sub_mode=p</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -969,40 +969,40 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026년 제1회 강원특별자치도 건축물미술작품 심의위원회 심의결과 공고</t>
+          <t>2026�� �뱸�����ü��������� ȯ�� �ü���� �Ⱓ���ٷ��� ����ä�� �����հݿ����� ��ǥ �� ä���ĺ�</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경기도_고양시</t>
+          <t>부산시설관리공단</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
+          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>『2026년 고양IR데이 운영 용역』 제안서 평가위원(후보자)모집 공고</t>
+          <t>부산시민공원 잔디밭 도서관 실행 용역 제안서 평가위원 후보자 공개모집 공고</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1026,28 +1026,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경남고시공고</t>
+          <t>경북고시공고</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
+          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=0</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1059,40 +1059,40 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026년 금원산산림자원관리소 숲해설 운영사업 제안서 평가결과 공개</t>
+          <t>2026년 「경북형 마이스 유치지원 및 홍보 」사업 보조사업자 선정결과 공고</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대구시설관리공단</t>
+          <t>전북도로관리사업소</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.dpfc.or.kr/sub.php?page_mode=board&amp;Page1=6&amp;Page2=5&amp;Page3=1&amp;Page4=0&amp;sub_mode=p</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1104,35 +1104,35 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026�� �뱸�����ü��������� ȯ�� �ü���� �Ⱓ���ٷ��� ����ä�� �����հݿ����� ��ǥ �� ä���ĺ�</t>
+          <t>복흥119지역대 신축 건축공사</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>부산시설관리공단</t>
+          <t>전남고시공고</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.bisco.or.kr/news/news01/index.asp</t>
+          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1149,7 +1149,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>부산시민공원 잔디밭 도서관 실행 용역 제안서 평가위원 후보자 공개모집 공고</t>
+          <t>2026년 국고보조사업 장애인 집합정보화 교육기관 선정결과 공고2026-03-06</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1161,28 +1161,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>전남고시공고</t>
+          <t>경기도_고양시</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.jeonnam.go.kr/J0203/boardList.do?menuId=jeonnam0203000000&amp;pageIndex=1</t>
+          <t>https://eminwon.goyang.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;not_ancmt_se_code=01,04,05&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;initValue=Y&amp;countYn=Y&amp;epcCheck=Y&amp;yyyymmdd=&amp;ofr_pageSize=60</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1194,7 +1194,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026년 국고보조사업 장애인 집합정보화 교육기관 선정결과 공고2026-03-06</t>
+          <t>『2026년 고양IR데이 운영 용역』 제안서 평가위원(후보자)모집 공고</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1206,28 +1206,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>전북도로관리사업소</t>
+          <t>경남도로관리사업소</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://www.gyeongnam.go.kr/street/board/list.gyeong?boardId=BBS_0000020&amp;menuCd=DOM_000000704001000000&amp;contentsSid=239&amp;cpath=%2Fstreet</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1239,24 +1239,24 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>복흥119지역대 신축 건축공사</t>
+          <t>교량 인상공법 공법제안서 제출안내 공고(국도24호선 남강교 내진..</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>경북고시공고</t>
+          <t>전북고시공고</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.gb.go.kr/Main/page.do?mnu_uid=6789&amp;LARGE_CODE=720&amp;MEDIUM_CODE=50&amp;SMALL_CODE=10&amp;SMALL_CODE2=30&amp;Start=10</t>
+          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1284,28 +1284,28 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026년 「경북 관광페스타 in 서울 행사 대행 용역」 제안서 평가위원회 예비평가 위원 모집 공고</t>
+          <t>복흥119지역대 신축 건축공사</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>전북고시공고</t>
+          <t>충북고시공고</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.jeonbuk.go.kr/board/list.jeonbuk?boardId=BBS_0000129&amp;menuCd=DOM_000000102002005000&amp;contentsSid=1379&amp;cpath=&amp;startPage=2</t>
+          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
@@ -1329,7 +1329,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>복흥119지역대 신축 건축공사</t>
+          <t>위임국도19호선 괴산 광덕리 도로확포장공사 신기술·특정공법 선정 안내 공고</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1341,23 +1341,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>경기도_군포시</t>
+          <t>경남고시공고</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
+          <t>https://www.gyeongnam.go.kr/index.gyeong?menuCd=DOM_000000135003009001&amp;pageLine=90</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>90</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1374,12 +1374,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026년 주민참여예산 제안사업 공모 공고</t>
+          <t>2026년 금원산산림자원관리소 숲해설 운영사업 제안서 평가결과 공개</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -1431,76 +1431,76 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>경기도_양주시</t>
+          <t>경기도_군포시</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.yangju.go.kr/www/selectBbsNttList.do?bbsNo=13&amp;key=202</t>
+          <t>https://gunpo.go.kr/www/selectEminwonNoticeList.do?key=3907&amp;Not_ancmt_se_code=01&amp;list_gubun=N&amp;ofr_pageSize=10&amp;notAncmtSeCd=01&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>스킵(IP차단된듯)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026년 주민참여예산 제안사업 공모 공고</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>충북고시공고</t>
+          <t>경기도_양주시</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.chungbuk.go.kr/www/selectGosiPblancList.do?key=422&amp;pageIndex=3</t>
+          <t>https://www.yangju.go.kr/www/selectBbsNttList.do?bbsNo=13&amp;key=202</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단된듯)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>위임국도19호선 괴산 광덕리 도로확포장공사 신기술·특정공법 선정 안내 공고</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1538,7 +1538,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026년 사회공익 승마사업 대상자 모집 공고</t>
+          <t>어린이집 운영비 보조금 반납명령 미이행에 따른 공시송달 공고</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1595,28 +1595,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>경기도_오산시</t>
+          <t>울산광역시고시공고</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
+          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=5</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1628,12 +1628,12 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026년 다문화가족 자녀 방문학습지 대상자 모집 공고</t>
+          <t>수의계약 견적제출 공고 - 2026년 공공하수처리시설 보수공사 실시설계용역</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -1685,28 +1685,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>울산광역시고시공고</t>
+          <t>경기도_오산시</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.ulsan.go.kr/u/rep/transfer/notice/list.ulsan?mId=001004002000000000&amp;curPage=5</t>
+          <t>https://www.osan.go.kr/portal/saeol/gosi/list.do?mId=0302010000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1718,35 +1718,35 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>수의계약 견적제출 공고 - 2026년 공공하수처리시설 보수공사 실시설계용역</t>
+          <t>2026년 다문화가족 자녀 방문학습지 대상자 모집 공고</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>경기도_동두천시</t>
+          <t>부산광역시고시공고</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.ddc.go.kr/ddc/selectGosiList.do?key=340&amp;not_ancmt_se_code=04&amp;pageIndex=2</t>
+          <t>https://www.busan.go.kr/nbgosi?curPage=5</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1763,7 +1763,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>가축(육용종계 및 육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
+          <t>「부산광역시 외국인주민정책 기본계획 수립 연구 용역」 제안서 기술능력(정성) 평가결과 공고</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1775,23 +1775,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>부산광역시고시공고</t>
+          <t>경기도_동두천시</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.busan.go.kr/nbgosi?curPage=5</t>
+          <t>https://www.ddc.go.kr/ddc/selectGosiList.do?key=340&amp;not_ancmt_se_code=04&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1808,7 +1808,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>「부산광역시 외국인주민정책 기본계획 수립 연구 용역」 제안서 기술능력(정성) 평가결과 공고</t>
+          <t>가축(육용종계 및 육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -1820,23 +1820,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>경기도_연천군</t>
+          <t>충남도로관리사업소</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
+          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>50</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1853,35 +1853,35 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>연천 전곡리 유적 세계유산 잠정목록 등재를 위한 연구 용역 제안서 평가 결과 공개</t>
+          <t>수의견적 제출 안내 공고(2026년 [논산]국지도68호 강경천교 보수보강공사)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>강원도_삼척시</t>
+          <t>경기도_연천군</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
+          <t>https://www.yeoncheon.go.kr/www/selectGosiList.do?key=3393&amp;not_ancmt_se_code=01&amp;pageUnit=50</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1898,7 +1898,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>고등 졸업학력 검정고시반 강사 모집 공고</t>
+          <t>연천 전곡리 유적 세계유산 잠정목록 등재를 위한 연구 용역 제안서 평가 결과 공개</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>충남도로관리사업소</t>
+          <t>충남고시공고</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1943,12 +1943,12 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>수의견적 제출 안내 공고(2026년 [논산]국지도68호 강경천교 보수보강공사)</t>
+          <t>「공인중개사 연수교육 영상 콘텐츠 제작 용역」 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>강원도_태백시</t>
+          <t>강원도_삼척시</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
+          <t>https://www.samcheok.go.kr/media/00084/00095.web?&amp;cpage=2</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2033,7 +2033,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>태백시 메이커AI 교육센터 운영 용역 제안서 평가위원(후보자) 모집 공고</t>
+          <t>고등 졸업학력 검정고시반 강사 모집 공고</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2045,16 +2045,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>경기도_양평군</t>
+          <t>강원도_원주시</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
+          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D39" t="n">
         <v>3</v>
@@ -2078,31 +2078,31 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026년 양평군 조직진단 연구용역 제안서 평가위원회 평가결과 공고</t>
+          <t>「2026년 혁신도시 문화행사(버스킹) 운영 대행 용역」기술제안서 평가결과 공개</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>충남고시공고</t>
+          <t>경기도_화성시</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.chungnam.go.kr/cnportal/province/province/list.do?menuNo=500487&amp;pageIndex=5</t>
+          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2123,7 +2123,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>「공인중개사 연수교육 영상 콘텐츠 제작 용역」 제안서 평가위원(후보자) 모집 공고</t>
+          <t>2026년 매향리평화기념관 제2회 기획전시 설계·제작·설치 용역 제안서 ...</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2135,23 +2135,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>강원도_영월군</t>
+          <t>경기도_수원시</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
+          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=5</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2168,7 +2168,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>「영월군 도로기반 지하시설물 전산화사업(산솔면)」 제안서 평가위원(후보자) 모집공고새글</t>
+          <t>민간임대주택에 관한 특별법 위반 과태료 체납 독촉 반송에 따른 공시송달 공고</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2180,19 +2180,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>경기도_화성시</t>
+          <t>강원도_태백시</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://eminwon.hscity.go.kr/emwp/gov/mogaha/ntis/web/ofr/action/OfrAction.do?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;not_ancmt_mgt_no=&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=80&amp;not_ancmt_se_code=01%2C04&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;cgg_code=&amp;not_ancmt_reg_no=&amp;cha_dep_code_nm=&amp;yyyy=2024&amp;Key=B_Subject&amp;temp=</t>
+          <t>https://www.taebaek.go.kr/www/selectBbsNttList.do?bbsNo=25&amp;key=352&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2213,7 +2213,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026년 매향리평화기념관 제2회 기획전시 설계·제작·설치 용역 제안서 ...</t>
+          <t>태백시 메이커AI 교육센터 운영 용역 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2225,28 +2225,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>경기도_포천시</t>
+          <t>강원도_인제군</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
+          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2258,28 +2258,28 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>포천시 농업기술센터 공고 제2026-145호포천 고병원성AI 발생(축O종계장) 관련 방역대 내 농가 이동제한 및 소독명령</t>
+          <t>2026년 제1차 경관위원회 심의결과 공고</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>강원도_원주시</t>
+          <t>경기도_양평군</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.wonju.go.kr/www/selectBbsNttList.do?bbsNo=140&amp;key=216&amp;pageUnit=40</t>
+          <t>https://www.yp21.go.kr/www/selectBbsNttList.do?bbsNo=5&amp;key=1119&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D44" t="n">
         <v>3</v>
@@ -2303,35 +2303,35 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>「2026년 혁신도시 문화행사(버스킹) 운영 대행 용역」기술제안서 평가결과 공개</t>
+          <t>2026년 양평군 조직진단 연구용역 제안서 평가위원회 평가결과 공고</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>경기도_수원시</t>
+          <t>강원도_평창군</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.suwon.go.kr/web/saeallOfr/BD_ofrList.do?q_currPage=5</t>
+          <t>https://www.pc.go.kr/portal/government/government-notification</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2348,7 +2348,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>민간임대주택에 관한 특별법 위반 과태료 체납 독촉 반송에 따른 공시송달 공고</t>
+          <t>「2026년 평창군 자기주도학습 지원 사업 운영 용역」제안서 정성적 평가 결과 공고</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2360,16 +2360,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>강원도_평창군</t>
+          <t>강원도_영월군</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.pc.go.kr/portal/government/government-notification</t>
+          <t>https://www.yw.go.kr/www/selectBbsNttList.do?bbsNo=17&amp;key=273&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D46" t="n">
         <v>3</v>
@@ -2393,7 +2393,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>「2026년 평창군 자기주도학습 지원 사업 운영 용역」제안서 정성적 평가 결과 공고</t>
+          <t>「영월군 도로기반 지하시설물 전산화사업(산솔면)」 제안서 평가위원(후보자) 모집공고</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2405,23 +2405,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>강원도_인제군</t>
+          <t>충청도_충주시</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.inje.go.kr/portal/adm/bulletin/notify</t>
+          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2438,12 +2438,12 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026년 제1차 경관위원회 심의결과 공고</t>
+          <t>단월 재해위험개선지구 정비사업 특정공법 선정 기술제안서 제출안내 재공고</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -2495,23 +2495,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>경기도_과천시</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2528,7 +2528,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>도시계획시설(체육시설:승마경기장)사업 실시계획인가 전 열람 · 공고</t>
+          <t>소규모 위험시설 지정 고시(주미동 소교량 외 28건)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2540,23 +2540,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>충청도_충주시</t>
+          <t>충청도_제천시</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.chungju.go.kr/www/selectEminwonList.do?key=510&amp;ofr_pageSize=90&amp;ancmt_se_code=01,02,04&amp;pageIndex=1</t>
+          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2573,7 +2573,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>단월 재해위험개선지구 정비사업 특정공법 선정 기술제안서 제출안내 재공고</t>
+          <t>장선천 하천기본계획(재수립)을 위한 전략환경영향평가 항목 등의 결정내용 공고새글</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -2585,23 +2585,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>경기도_가평군</t>
+          <t>경기도_과천시</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=5</t>
+          <t>https://www.gccity.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2618,35 +2618,35 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>제20회 경기도장애인생활체육대회 및 제37회 경기도생활체육대축전 개・폐회식 연출대행 용역 제안서 평가위원(후보자) 모집 변경 공고</t>
+          <t>도시계획시설(체육시설:승마경기장)사업 실시계획인가 전 열람 · 공고</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>경기도_여주시</t>
+          <t>충청도_공주시</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=3</t>
+          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2663,12 +2663,12 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026년 마을공동체 주민제안 공모사업 선정...</t>
+          <t>공주시 충남형 농촌리브투게더 신풍지구 임대주택 입주자 추가 모집 공고(8차)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -2720,16 +2720,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>충청도_제천시</t>
+          <t>경기도_가평군</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.jecheon.go.kr/www/selectBbsNttList.do?bbsNo=18&amp;key=5233&amp;pageIndex=2</t>
+          <t>https://www.gp.go.kr/portal/selectGosiList.do?key=2148&amp;not_ancmt_se_code=01&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D54" t="n">
         <v>3</v>
@@ -2753,35 +2753,35 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>장선천 하천기본계획(재수립)을 위한 전략환경영향평가 항목 등의 결정내용 공고새글</t>
+          <t>제20회 경기도장애인생활체육대회 및 제37회 경기도생활체육대축전 개・폐회식 연출대행 용역 제안서 평가위원(후보자) 모집 변경 공고</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>충청도_옥천군</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_01/sub04_03_01/list.do</t>
+          <t>https://www.oc.go.kr/www/selectBbsNttList.do?bbsNo=40&amp;key=236&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2798,7 +2798,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>소규모 위험시설 지정 고시(주미동 소교량 외 28건)</t>
+          <t>가축 등에 대한 일시 이동중지 명령(육계 및 육용종계)새글</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -2810,12 +2810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>충청도_옥천군</t>
+          <t>강원도_횡성군</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.oc.go.kr/www/selectBbsNttList.do?bbsNo=40&amp;key=236&amp;pageIndex=2</t>
+          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2843,7 +2843,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>가축 등에 대한 일시 이동중지 명령(육계 및 육용종계)새글</t>
+          <t>154kV 북원주-횡성 기설송전선로 권원확보사업[4차] 전원개발사업 실시계획 변경승인 및 사업인정에 관한 주민 등의 의견청취 공고</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -2855,73 +2855,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>강원도_횡성군</t>
+          <t>전라도_남원시</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.hsg.go.kr/www/selectBbsNttList.do?bbsNo=65&amp;key=821&amp;pageIndex=2</t>
+          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>154kV 북원주-횡성 기설송전선로 권원확보사업[4차] 전원개발사업 실시계획 변경승인 및 사업인정에 관한 주민 등의 의견청취 공고</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>경기도_시흥시</t>
+          <t>충청도_부여군</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
+          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2933,69 +2917,85 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>가축 등에 대한 일시 이동중지 명령</t>
+          <t>「부여군 매장문화재 유존지역 정보고도화 사업 지도 제작 및 DB 구축 용역」 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2024-04-17</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>전라도_남원시</t>
+          <t>충청도_보령시</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.namwon.go.kr/board/post/list.do?boardUid=ff8080818ea1fec5018ea24137680031&amp;menuUid=ff8080818e3beff0018e4077131b007a</t>
+          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>가축(육용종계, 육계) 등에 대한 일시이동중지(Standstill) 명령 알림(경기 포천 HPAI)</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>충청도_보령시</t>
+          <t>충청도_예산군</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.brcn.go.kr/prog/eminwon/kor/BB/sub04_03_01/list.do?pageIndex=2</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>20</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3007,40 +3007,40 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>가축(육용종계, 육계) 등에 대한 일시이동중지(Standstill) 명령 알림(경기 포천 HPAI)</t>
+          <t>구)충남방적부지개발사업 기본구상 및 타당성조사용역 제안서 평가결과</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>충청도_공주시</t>
+          <t>경기도_시흥시</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.gongju.go.kr/prog/saeolGosi/GOSI_03/sub04_03_03/list.do</t>
+          <t>https://www.siheung.go.kr/main/saeol/gosi/list.do?mId=0401040100</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3052,24 +3052,24 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>공주시 충남형 농촌리브투게더 신풍지구 임대주택 입주자 추가 모집 공고(8차)</t>
+          <t>가축 등에 대한 일시 이동중지 명령</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>전라도_김제시</t>
+          <t>전라도_부안군</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3097,40 +3097,40 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>자동차 편취말소 예고 통지에 따른 고시공고</t>
+          <t>도로기반 지하시설물 전산화 확산사업 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>전라도_부안군</t>
+          <t>충청도_예산군</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.buan.go.kr/board/list.buan?boardId=BBS_0000054&amp;menuCd=DOM_000000103001003000&amp;contentsSid=84&amp;startPage=1</t>
+          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3142,40 +3142,40 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>도로기반 지하시설물 전산화 확산사업 제안서 평가위원(후보자) 모집 공고</t>
+          <t>2026년 봉수산 자연휴양림 데크보행로 교체사업 실시설계용역 수의(2인 이상) 견적제출 안내공고</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>충청도_예산군</t>
+          <t>충청도_금산군</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/GOSI/kor/sub04_03_01/list.do</t>
+          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20계속</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3187,35 +3187,35 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>구)충남방적부지개발사업 기본구상 및 타당성조사용역 제안서 평가결과</t>
+          <t>[일반공고]2026년 금산군 군민리포터 모집 공고</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20계속</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>충청도_예산군</t>
+          <t>전라도_강진군</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.yesan.go.kr/prog/saeolGosi/02/kor/sub04_03_03/list.do</t>
+          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3232,40 +3232,40 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026년 봉수산 자연휴양림 데크보행로 교체사업 실시설계용역 수의(2인 이상) 견적제출 안내공고</t>
+          <t>전기사업 양수인가 공고(해든 태양광발전소)새로운글</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>충청도_부여군</t>
+          <t>전라도_김제시</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.buyeo.go.kr/_prog/_board/?code=news_02&amp;site_dvs_cd=kr&amp;menu_dvs_cd=040205</t>
+          <t>https://www.gimje.go.kr/board/list.gimje?boardId=BBS_0000044&amp;menuCd=DOM_000000104003000000&amp;contentsSid=196&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D66" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3277,24 +3277,24 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>「부여군 매장문화재 유존지역 정보고도화 사업 지도 제작 및 DB 구축 용역」 제안서 평가위원(후보자) 모집 공고</t>
+          <t>자동차 편취말소 예고 통지에 따른 고시공고</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>전라도_강진군</t>
+          <t>전라도_무안군</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.gangjin.go.kr/www/government/notice/gosi?page=1</t>
+          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3322,7 +3322,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>전기사업 양수인가 공고(해든 태양광발전소)새로운글</t>
+          <t>2026 신도시주민 농업.농촌 체험 활동 추가 모집공고</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -3334,28 +3334,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>충청도_금산군</t>
+          <t>충청도_청주시</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.geumsan.go.kr/kr/html/sub03/030302.html?GotoPage=1</t>
+          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>20계속</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3367,28 +3367,28 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[일반공고]2026년 금산군 군민리포터 모집 공고</t>
+          <t>통장 선정 주민투표 공고(28통)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>20계속</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>전라도_무안군</t>
+          <t>충청도_음성군</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.muan.go.kr/www/openmuan/new/announcement?page=1</t>
+          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D69" t="n">
         <v>3</v>
@@ -3412,7 +3412,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026 신도시주민 농업.농촌 체험 활동 추가 모집공고</t>
+          <t>음성 그린에너지 스마트농업타운 투자선도지구 출자타당성 검토 용역 제안서 ...</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3424,28 +3424,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>충청도_청주시</t>
+          <t>전라도_보성군</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.cheongju.go.kr/www/selectEminwonNoticeList.do?key=23366&amp;notAncmtSeCd=&amp;searchCnd=all&amp;searchKrwd=&amp;pageIndex=5</t>
+          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3457,28 +3457,28 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>통장 선정 주민투표 공고(28통)</t>
+          <t>보성군 가축사육제한구역 지형도면 정정 변경고시새로운글</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>충청도_음성군</t>
+          <t>경기도_안산시</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.eumseong.go.kr/www/selectEminwonList.do?key=80&amp;pageUnit=10&amp;ofr_pageSize=10&amp;amp;not_ancmt_se_code=01,02,03,04,05&amp;pageIndex=5</t>
+          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D71" t="n">
         <v>3</v>
@@ -3502,7 +3502,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>음성 그린에너지 스마트농업타운 투자선도지구 출자타당성 검토 용역 제안서 ...</t>
+          <t>신규주민등록증 통지서 반송자 공고(2009년 2월생)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -3559,23 +3559,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>전라도_고창군</t>
+          <t>전라도_곡성군</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
+          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3592,7 +3592,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[43425]「고창갯벌 세계유산 OUV 공감 콘텐츠 용역」 제안서 평가 결과 공고첨부파일 있음</t>
+          <t>도로명주소 고시(2026-03-06)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -3604,23 +3604,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>전라도_곡성군</t>
+          <t>전라도_순천시</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.gokseong.go.kr/board/GosiList.do?menuNo=102001003000</t>
+          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=4</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3637,7 +3637,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>도로명주소 고시(2026-03-06)</t>
+          <t>2026년 순천만국가정원 관객참여형 디지털인형극 운영 용역 제안서 평가 ...</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3649,16 +3649,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>전라도_영광군</t>
+          <t>전라도_고창군</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
+          <t>https://www.gochang.go.kr/board/list.gochang?boardId=BBS_0000180&amp;menuCd=DOM_000000102003007000&amp;contentsSid=2682&amp;startPage=4</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D75" t="n">
         <v>3</v>
@@ -3682,7 +3682,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>영광읍 농촌중심지활성화사업 기본계획 승인 고시</t>
+          <t>[43425]「고창갯벌 세계유산 OUV 공감 콘텐츠 용역」 제안서 평가 결과 공고첨부파일 있음</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3694,28 +3694,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>전라도_진도군</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
+          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>10</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3727,40 +3727,40 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[고시]진도 군관리계획(문화공원 및 공원조성계획) 결정(변경) 지형도면 고시</t>
+          <t>제9회 전국동시지방선거 공정선거지원단(선거) 모집 안내</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>전라도_진도군</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/boardList.do?boardId=ORGAN&amp;pageId=www274</t>
+          <t>https://www.jindo.go.kr/home/gosi/general.cs?m=24&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>10</v>
       </c>
       <c r="D77" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3772,12 +3772,12 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>제9회 전국동시지방선거 공정선거지원단(선거) 모집 안내</t>
+          <t>[고시]진도 군관리계획(문화공원 및 공원조성계획) 결정(변경) 지형도면 고시</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -3829,16 +3829,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>경기도_안산시</t>
+          <t>전라도_영광군</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.ansan.go.kr/www/common/bbs/selectPageListBbs.do?bbs_code=WWW13&amp;currentPage=3</t>
+          <t>https://www.yeonggwang.go.kr/bbs/?b_id=gosigonggo&amp;site=headquarter_new&amp;mn=9059&amp;offset=15</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D79" t="n">
         <v>3</v>
@@ -3862,7 +3862,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>신규주민등록증 통지서 반송자 공고(2009년 2월생)</t>
+          <t>영광읍 농촌중심지활성화사업 기본계획 승인 고시</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -3919,24 +3919,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>전라도_신안군</t>
+          <t>전라도_장성군</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
+          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
-      </c>
-      <c r="E81" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3948,35 +3952,35 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026년 교통지원과 보조항로팀 기간제근로자 재공고</t>
+          <t>2026년 제2회 장성군 건축위원회(건축물해체분야) 심의결...</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>전라도_장성군</t>
+          <t>경상도_군위군</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.jangseong.go.kr/home/www/news/jangseong/announcement?page=2</t>
+          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3993,76 +3997,60 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026년 제2회 장성군 건축위원회(건축물해체분야) 심의결...</t>
+          <t>도로명주소 고시</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>대구광역시고시공고</t>
+          <t>경상도_울진군</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
+          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP 차단)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>「2026년 대구광역시 항공사진 촬영 용역」 제안서 평가위원회 평가위원(후보자) 모집 공고문</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>경상도_문경시</t>
+          <t>강원도_홍천군</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
+          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4071,7 +4059,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4083,43 +4071,59 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>「문경시 문화예술회관 안전난간 설치사업」신기술・특허공법 선정 기술제안서 제출기한 연장 안내 공고</t>
+          <t>지적측량기준점(도근점) 성과 고시</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>경상도_울진군</t>
+          <t>경상도_문경시</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.uljin.go.kr/index.uljin?menuCd=DOM_000000103002007000</t>
+          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>스킵(IP 차단)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>「문경시 문화예술회관 안전난간 설치사업」신기술・특허공법 선정 기술제안서 제출기한 연장 안내 공고</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4214,28 +4218,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>경상도_군위군</t>
+          <t>경상도_창원시_의창구</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.gunwi.go.kr/ko/page.do?mnu_uid=666&amp;pageNo=1</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>10</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4247,40 +4251,40 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>도로명주소 고시</t>
+          <t>[의창구 팔룡동] 여성민방위 기동대 민방위 비상급수 시설 점검</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>경상도_창원시_의창구</t>
+          <t>경상도_창원시_성산구</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11094/11462/11476.web?cpage=1</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>10</v>
       </c>
       <c r="D89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4292,40 +4296,40 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[의창구 팔룡동] 여성민방위 기동대 민방위 비상급수 시설 점검</t>
+          <t>성산구,「2026년 재가의료급여 사업」업무 협약체결</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>경상도_창원시_성산구</t>
+          <t>경상도_창원시_마산합포구</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11098/11607/11640.web</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>10</v>
       </c>
       <c r="D90" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4337,40 +4341,40 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>성산구,「2026년 재가의료급여 사업」업무 협약체결</t>
+          <t>마산합포구, 체납차량 번호판 집중 영치기간 운영</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산합포구</t>
+          <t>경상도_창원시_마산회원구</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11099/11806/11850.web</t>
+          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>10</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4382,35 +4386,35 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>마산합포구, 체납차량 번호판 집중 영치기간 운영새 글</t>
+          <t>(마산회원구 가정복지과) 한눈에, 한 손에, 한부모가족 복지안내서 제작·배부새 글</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>경상도_창원시_마산회원구</t>
+          <t>대구광역시고시공고</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/gu/11100/12100/12138.web?cpage=1</t>
+          <t>https://www.daegu.go.kr/index.do?menu_id=00940170</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4427,12 +4431,12 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>(마산회원구 가정복지과) 한눈에, 한 손에, 한부모가족 복지안내서 제작·배부새 글</t>
+          <t>「2026년 대구광역시 항공사진 촬영 용역」 제안서 평가위원회 평가위원(후보자) 모집 공고문</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
@@ -4529,28 +4533,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>충청도_홍성군</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
+          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D95" t="n">
         <v>3</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4562,35 +4566,35 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>전문건설업 등록(신규, 업종추가) 공고</t>
+          <t>정수장 일일수질검사 결과 안내(2026.3.6.)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>충청도_서산시</t>
+          <t>경상도_거제시</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
+          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4607,7 +4611,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>「서산시 2차 스마트도시계획 수립 용역」의 제안서 평가위원회 결과 공고</t>
+          <t>「거제식물원 열린관광 콘텐츠 기획 및 구축 용역」 제안서 평가결과 공고</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -4619,12 +4623,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=752&amp;pageid=1</t>
+          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -4635,12 +4639,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20새글</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4652,24 +4656,24 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>정수장 일일수질검사 결과 안내(2026.3.6.)</t>
+          <t>[일자리ㆍ기업]밀양시종합사회복지관 관장 채용 공고</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>20새글</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>전라도_광양시</t>
+          <t>충청도_홍성군</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
+          <t>https://www.hongseong.go.kr/prog/saeolGosi/kor/sub03_0204/GOSI_ALL/list.do</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -4697,7 +4701,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026년 숲생태관리인(숲해설가) 채용 공고</t>
+          <t>전문건설업 등록(신규, 업종추가) 공고</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4709,21 +4713,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>충청도_서산시</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=2</t>
+          <t>https://www.seosan.go.kr/common/program/eminwonView.jsp?pageIndex=&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;method=selectListOfrNotAncmt&amp;methodnm=selectListOfrNotAncmtHomepage&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;not_ancmt_se_code=01%2C04%2C06&amp;title=%EA%B3%A0%EC%8B%9C%EA%B3%B5%EA%B3%A0&amp;cha_dep_code_nm=&amp;initValue=&amp;countYn=Y&amp;list_gubun=&amp;not_ancmt_sj=&amp;not_ancmt_cn=&amp;dept_nm=&amp;mobile_code=00&amp;Key=B_Subject&amp;not_ancmt_mgt_no=&amp;temp=</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>20</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
-      </c>
-      <c r="E99" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -4738,37 +4746,33 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[종합소식]양육비 선지급제 안내새 글</t>
+          <t>「서산시 2차 스마트도시계획 수립 용역」의 제안서 평가위원회 결과 공고</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>경상도_사천시</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00024.web?gcode=1171&amp;cpage=2</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>20</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -4783,7 +4787,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[사천시 공고 제2026-449호]담배소매인(사망자)직권취소 및 지정신청 공고새 글</t>
+          <t>[종합소식]양육비 선지급제 안내새 글</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4795,23 +4799,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>경상도_사천시</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
+          <t>https://www.sacheon.go.kr/news/00009/00014.web?cpage=2</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4828,7 +4832,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2025년 성과관리 평가결과 공개</t>
+          <t>[사천시 공고 제2026-449호]담배소매인(사망자)직권취소 및 지정신청 공고새 글</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -4840,23 +4844,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>경상도_창원시</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=5</t>
+          <t>https://www.yangsan.go.kr/portal/board/post/list.do?bcIdx=293&amp;mid=0101010000</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4873,7 +4877,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
-          <t>『덕동생활폐기물매립장 2단계 조성사업』공법선정을 위한 공법선정위원회 평가위원(후보자) 모집 공고</t>
+          <t>2025년 성과관리 평가결과 공개</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -4885,19 +4889,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>경상도_김해시</t>
+          <t>경상도_창원시</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
+          <t>https://www.changwon.go.kr/cwportal/10310/10438/10439.web?&amp;cpage=5</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4906,7 +4910,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4918,7 +4922,7 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t>「주촌면 농촌중심지 활성화사업 기본계획수립 용역」제안서 평가결과 공고</t>
+          <t>『덕동생활폐기물매립장 2단계 조성사업』공법선정을 위한 공법선정위원회 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -4930,97 +4934,97 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_남해군_상주면</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/bbs/selectNoticeList.do?mnNo=20901000000&amp;owd=&amp;searchCnd=&amp;searchWrd=&amp;searchCateId=&amp;pageIndex=2</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%83%81%EC%A3%BC%EB%A9%B4&amp;pageCd=WW0512040402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>20새글</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP 차단)</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>[일자리ㆍ기업]「2026년 소상공인 온라인 입점 지원사업」  참여 소상공인 모집 공고 안내새글</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>20새글</t>
-        </is>
-      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>경상도_남해군_상주면</t>
+          <t>전라도_광양시</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%83%81%EC%A3%BC%EB%A9%B4&amp;pageCd=WW0512040402&amp;siteGubun=portal</t>
+          <t>https://gwangyang.go.kr/saeol/gosi.es?mid=a11005020000&amp;type_code=02,04</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>스킵(IP 차단)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026년 숲생태관리인(숲해설가) 채용 공고</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>경상도_거제시</t>
+          <t>경상도_의령군</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.geoje.go.kr/index.geoje?menuCd=DOM_000008902001002001&amp;listRow=90</t>
+          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5037,40 +5041,40 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>「거제식물원 열린관광 콘텐츠 기획 및 구축 용역」 제안서 평가결과 공고</t>
+          <t>전문건설업 신규등록 공고</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>경상도_의령군</t>
+          <t>경상도_김해시</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.uiryeong.go.kr/board/list.uiryeong?boardId=BBS_0000070&amp;menuCd=DOM_000000203003001001&amp;contentsSid=201&amp;startPage=1</t>
+          <t>https://www.gimhae.go.kr/03360/00023/00029.web?&amp;cpage=4</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D107" t="n">
         <v>3</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5082,7 +5086,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>전문건설업 신규등록 공고</t>
+          <t>「주촌면 농촌중심지 활성화사업 기본계획수립 용역」제안서 평가결과 공고</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5094,16 +5098,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>전라도_순천시</t>
+          <t>경상도_통영시</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>http://www.suncheon.go.kr/kr/news/0004/0005/0001/?x=1&amp;pageIndex=4</t>
+          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D108" t="n">
         <v>3</v>
@@ -5127,40 +5131,40 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026년 순천만국가정원 관객참여형 디지털인형극 운영 용역 제안서 평가 ...</t>
+          <t>통영 수산업・어촌 발전 기본계획 수립 연구용역 제안서 평가위원회 결과 공고</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>경상도_통영시</t>
+          <t>경상도_함안군</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.tongyeong.go.kr/00852/00853/00858.web?&amp;cpage=3</t>
+          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D109" t="n">
         <v>3</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5172,24 +5176,24 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>통영 수산업・어촌 발전 기본계획 수립 연구용역 제안서 평가위원회 결과 공고</t>
+          <t>2026년 함안문화예술회관 「유아 문화예술교육 지원사업」 문화예술교육단체 모집 공고</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>전라도_영암군</t>
+          <t>경상도_하동군</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
+          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -5217,7 +5221,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>도로명주소 부여 고시</t>
+          <t>경기도 포천시 AI발생 관련 가축(육용종계,육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5229,86 +5233,86 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>경상도_함안군</t>
+          <t>경상도_남해군_서면</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.haman.go.kr/00960/00962.web?&amp;cpage=1</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP 차단)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>2026년 함안문화예술회관 「유아 문화예술교육 지원사업」 문화예술교육단체 모집 공고</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>경상도_남해군_서면</t>
+          <t>전라도_영암군</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%9C%EB%A9%B4&amp;pageCd=WW0512080402&amp;siteGubun=portal</t>
+          <t>https://www.yeongam.go.kr/home/www/open_information/yeongam_news/announcement/yeongam.go?page=3</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>스킵(IP 차단)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>도로명주소 부여 고시</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>경상도_하동군</t>
+          <t>경상도_밀양시</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.hadong.go.kr/media/00012.web?cpage=3</t>
+          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -5336,7 +5340,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>경기도 포천시 AI발생 관련 가축(육용종계,육계) 등에 대한 일시 이동중지(Standstill) 명령 발령 알림</t>
+          <t>밀양시 2030's 미래농업 프로젝트 추진계획 용역 제안서 평...</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -5348,28 +5352,28 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>경상도_남해군_설천면</t>
+          <t>경상도_거창군</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
+          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D114" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5381,12 +5385,12 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(설천면)</t>
+          <t>제292회 거창군의회 임시회 집회 공고</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -5438,23 +5442,23 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>경상도_남해군_미조면</t>
+          <t>경상도_남해군_이동면</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>10</v>
       </c>
       <c r="D116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5471,7 +5475,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2026년 미조면 취약해안폐기물 대응사업 채용공고</t>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(이동면)</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -5483,12 +5487,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>경상도_남해군_삼동면</t>
+          <t>경상도_남해군_창선면</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5499,12 +5503,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5516,24 +5520,24 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026년 삼동다락생활문화센터 프로그램 수강생 모집 공고(수정)</t>
+          <t>2026년 창선면 해양쓰레기 정화사업(구 바다환경지킴이)기간제근로자 채용 안내</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>경상도_남해군_이동면</t>
+          <t>경상도_남해군_삼동면</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%9D%B4%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512030402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%82%BC%EB%8F%99%EB%A9%B4&amp;pageCd=WW0512050402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -5549,7 +5553,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5561,40 +5565,40 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(이동면)</t>
+          <t>2026년 삼동다락생활문화센터 프로그램 수강생 모집 공고(수정)</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>경상도_남해군_남면</t>
+          <t>경상도_남해군_미조면</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%AF%B8%EC%A1%B0%EB%A9%B4&amp;pageCd=WW0512060402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>10</v>
       </c>
       <c r="D119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5606,24 +5610,24 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(남면)</t>
+          <t>2026년 미조면 취약해안폐기물 대응사업 채용공고</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>경상도_남해군_고현면</t>
+          <t>경상도_남해군_남면</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EA%B3%A0%ED%98%84%EB%A9%B4&amp;pageCd=WW0512090402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EB%82%A8%EB%A9%B4&amp;pageCd=WW0512070402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5634,12 +5638,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5651,24 +5655,24 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>제3기 고현면 주민자치회 위원 명단 공개</t>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(남면)</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>경상도_남해군_창선면</t>
+          <t>경상도_남해군_고현면</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%B0%BD%EC%84%A0%EB%A9%B4&amp;pageCd=WW0512110402&amp;siteGubun=portal</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EA%B3%A0%ED%98%84%EB%A9%B4&amp;pageCd=WW0512090402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -5679,7 +5683,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5696,7 +5700,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>2026년 창선면 해양쓰레기 정화사업(구 바다환경지킴이)기간제근로자 채용 안내</t>
+          <t>제3기 고현면 주민자치회 위원 명단 공개</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -5708,28 +5712,28 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>경상도_밀양시</t>
+          <t>경상도_남해군_설천면</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.miryang.go.kr/web/eMinwonList.do?mnNo=20903000000&amp;pageIndex=3</t>
+          <t>https://www.namhae.go.kr/modules/saeol/gosi.do?dep_nm=%EC%84%A4%EC%B2%9C%EB%A9%B4&amp;pageCd=WW0512100402&amp;siteGubun=portal</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D122" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5741,35 +5745,35 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>밀양시 2030's 미래농업 프로젝트 추진계획 용역 제안서 평...</t>
+          <t>2026년 취약해안폐기물 대응사업 기간제근로자 채용 공고(설천면)</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>경상도_거창군</t>
+          <t>경상도_양산시</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.geochang.go.kr/saeol/gosi.do?pageCd=NW0102000000&amp;siteGubun=news&amp;cpage=4</t>
+          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5779,59 +5783,43 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>실패(타임아웃)</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>타임아웃</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>제292회 거창군의회 임시회 집회 공고</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>경상도_양산시</t>
+          <t>광주도시관리공사</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.yangsan.go.kr/portal/saeol/gosi/list.do?mid=0102010000</t>
+          <t>https://www.gumc.or.kr/news/bidding</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>스킵(fail)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -5873,7 +5861,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/bidding</t>
+          <t>https://www.gumc.or.kr/news/news</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -5897,41 +5885,53 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>광주도시관리공사</t>
+          <t>세종소개공고</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.gumc.or.kr/news/news</t>
+          <t>https://www.sejong.go.kr/prog/publicNotice/kor/sub02_0303/C1/list.do</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2026년 제54회 어버이날 공모선정 결과</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>세종소개공고</t>
+          <t>경기도_수원_팔달구</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.sejong.go.kr/prog/publicNotice/kor/sub02_0303/C1/list.do</t>
+          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -5940,7 +5940,11 @@
       <c r="D128" t="n">
         <v>3</v>
       </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -5955,7 +5959,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
-          <t>2026년 제54회 어버이날 공모선정 결과</t>
+          <t>장애인전용주차구역 주차위반 압류통지 반송분 공시송달 공고</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -6008,23 +6012,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>경기도_수원_팔달구</t>
+          <t>경기도_수원_권선구</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>http://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3770000&amp;epcCheck=Y</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6034,21 +6038,17 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>실패(타임아웃)</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>타임아웃</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>장애인전용주차구역 주차위반 압류통지 반송분 공시송달 공고</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6184,28 +6184,28 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>경기도_수원_권선구</t>
+          <t>경기도_광주시</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=3760000&amp;epcCheck=Y</t>
+          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D134" t="n">
         <v>3</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -6217,35 +6217,35 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
-          <t>이륜자동차 정기검사 신청기간 경과 알림 및 명령서 반송분 공시송달 공고</t>
+          <t>가축 등에 대한 일시 이동중지 명령(AI)_경기 포천새 글</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>경기도_부천시</t>
+          <t>대전광역시고시공고</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
+          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6262,7 +6262,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
-          <t>2026년 마을공동체 활동매니저 합격자 공고</t>
+          <t>제안서 평가위원 공개모집 재공고(성북동체육공원 파크골프장 조성 타당성 조사 및 기본계획 수립용역)</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -6274,19 +6274,19 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>대전광역시고시공고</t>
+          <t>경기고시공고</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.daejeon.go.kr/drh/drhGosiList.do?gosigbn=A&amp;menuSeq=1908</t>
+          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=4</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>40</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -6295,43 +6295,47 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>『3기 신도시 리츠 도입 연구용역 2건』제안서 평가위원 후보자 공개모집</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>경기도_광주시</t>
+          <t>경기도_성남시수정구</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.gjcity.go.kr/portal/saeol/gosi/list.do?mId=0202010000&amp;token=1688448678130</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6341,31 +6345,35 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>무단방치차량 강제처리(폐차) 및 이해관계인 권리행사 공고</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>경기도_성남시수정구</t>
+          <t>경기도_안양시</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3790000&amp;not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D138" t="n">
         <v>3</v>
@@ -6389,35 +6397,35 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
-          <t>무단방치차량 강제처리(폐차) 및 이해관계인 권리행사 공고</t>
+          <t>「박달동 및 인덕원동 하수도정비 중점관리지역 도시침수예방사업」공법선정평가위원회 평가위원(후보자) 공개모집 공고</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>경기도_안양시</t>
+          <t>경기도_용인시처인구</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.anyang.go.kr/main/emwsWebList.do?key=4101&amp;searchGosiSe=01,03,04&amp;pageUnit=40</t>
+          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6434,28 +6442,28 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
-          <t>「박달동 및 인덕원동 하수도정비 중점관리지역 도시침수예방사업」공법선정평가위원회 평가위원(후보자) 공개모집 공고</t>
+          <t>무단 방치자전거 보관 및 처분 공고</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>경기고시공고</t>
+          <t>경기도_부천시</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.gg.go.kr/bbs/board.do?bsIdx=469&amp;menuId=1547#page=5</t>
+          <t>https://eminwon.bucheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?epcCheck=Y</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D140" t="n">
         <v>2</v>
@@ -6479,7 +6487,7 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
-          <t>『3기 신도시 리츠 도입 연구용역 2건』제안서 평가위원 후보자 공개모집</t>
+          <t>2026년 마을공동체 활동매니저 합격자 공고</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -6532,23 +6540,23 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>경기도_성남시중원구</t>
+          <t>경기도_이천시</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
+          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6565,7 +6573,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>무단방치 이륜차 자진처리명령서 공시송달 및 강제처리(폐차) 공고</t>
+          <t>도로명주고 부여 고시</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -6577,23 +6585,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>경기도_이천시</t>
+          <t>경기도_성남시</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.icheon.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0402010000&amp;token=1707785005520</t>
+          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6610,7 +6618,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>도로명주고 부여 고시</t>
+          <t>도로명주소(건물번호) 부여 고시</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -6667,23 +6675,23 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>경기도_성남시</t>
+          <t>강원도_동해시</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6700,12 +6708,12 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>도로명주소(건물번호) 부여 고시</t>
+          <t>「동해시 교육발전 중장기 기본계획 수립 연구 용역」 제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -6757,28 +6765,28 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>강원도_동해시</t>
+          <t>경기도_평택시</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.dh.go.kr/www/selectBbsNttList.do?bbsNo=87&amp;key=478&amp;recordCountPerPage=90</t>
+          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D147" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6790,40 +6798,40 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>「동해시 교육발전 중장기 기본계획 수립 연구 용역」 제안서 평가위원(후보자) 모집 공고</t>
+          <t>주민등록 장기 거주불명자 최고 공고</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>경기도_평택시</t>
+          <t>강원도_속초시</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.pyeongtaek.go.kr/pyeongtaek/saeol/gosi/list.do?mid=0401020100</t>
+          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6835,35 +6843,35 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>주민등록 장기 거주불명자 최고 공고</t>
+          <t>속초 도시계획시설(도로: 중로3-35호선) 실시계획인가(변경) 고시</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>강원도_양구군</t>
+          <t>강원도_강릉시</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
+          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=3</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D149" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6880,28 +6888,28 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[양구군 공고 제2026-228호] 수입천 오지마을 시끌벅적 활성화 사업 건축설계공모(제안공모) 서면질의         ...</t>
+          <t>2026년도 경포동 환경관리원 대체인력(기간제근로자) 채용 합격자 공고</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>강원도_속초시</t>
+          <t>강원도_고성군</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.sokcho.go.kr/sc/portal/sokchonews/notification</t>
+          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D150" t="n">
         <v>4</v>
@@ -6925,28 +6933,28 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
-          <t>속초 도시계획시설(도로: 중로3-35호선) 실시계획인가(변경) 고시</t>
+          <t>고성군 친환경로컬푸드매장 관리위탁 제안서 제출안내 및 입찰공고(재공고)</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>강원도_강릉시</t>
+          <t>경기도_안성시</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.gn.go.kr/www/selectGosiNttList.do?key=263&amp;searchGosiSe=01,04,06&amp;pageIndex=3</t>
+          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D151" t="n">
         <v>3</v>
@@ -6970,7 +6978,7 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
-          <t>2026년도 경포동 환경관리원 대체인력(기간제근로자) 채용 합격자 공고</t>
+          <t>공도 도시계획시설(공공ㆍ문화체육시설: 문화 및 사회복지시설-공도시민청) 실시계획(변경)작성 고시</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -6982,23 +6990,23 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>강원도_고성군</t>
+          <t>강원도_양구군</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://eminwon.gwgs.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04</t>
+          <t>https://www.yanggu.go.kr/user_sub?gfnc=www&amp;mu_idx=226&amp;pgsize=100</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="D152" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7015,24 +7023,24 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
-          <t>고성군 친환경로컬푸드매장 관리위탁 제안서 제출안내 및 입찰공고(재공고)</t>
+          <t>[양구군 공고 제2026-228호] 수입천 오지마을 시끌벅적 활성화 사업 건축설계공모(제안공모) 서면질의         ...</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>경기도_안성시</t>
+          <t>경기도_파주시</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.anseong.go.kr/portal/saeol/gosiList.do?mId=0501040000&amp;token=1717572030185</t>
+          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -7060,7 +7068,7 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
-          <t>공도 도시계획시설(공공ㆍ문화체육시설: 문화 및 사회복지시설-공도시민청) 실시계획(변경)작성 고시</t>
+          <t>파랑해 이벤트 Vol. 1 「내가 그린 파랑, 띠-부 스티커가로 태어나다!」 새학기 맞이 공모이벤트N</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -7117,97 +7125,97 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>경기도_파주시</t>
+          <t>충청도_청주시_서원구</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://dong.paju.go.kr/dong/user/board/BD_board.list.do?bbsCd=1022&amp;q_ctgCd=4063</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(IP차단)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>파랑해 이벤트 Vol. 1 「내가 그린 파랑, 띠-부 스티커가로 태어나다!」 새학기 맞이 공모이벤트N</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>충청도_청주시_서원구</t>
+          <t>충청도_괴산군</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020&amp;cha_dep_code_nm=57250210000,57250220000,57250040000,57250270000,57250060000,57250070000,57250280000,57250090000</t>
+          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>스킵(IP차단)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>도로명주소 고시</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>충청도_괴산군</t>
+          <t>강원도_양양군</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://eminwon.goesan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7224,7 +7232,7 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>도로명주소 고시</t>
+          <t>「행정재산 실태조사 및 공유재산 통합 DB구축 용역」 제안서 평가위원회 평가 결과 공고</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -7281,28 +7289,28 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>강원도_양양군</t>
+          <t>충청도_보은군</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://eminwon.yangyang.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D159" t="n">
         <v>3</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -7314,40 +7322,40 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>「행정재산 실태조사 및 공유재산 통합 DB구축 용역」 제안서 평가위원회 평가 결과 공고</t>
+          <t>경기 포천 육용종계농장 고병원성 조류인플루엔자 발생관련 가축(육용종계, 육계) 등에 대한 일시이동중지 명령 알림</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>충청도_보은군</t>
+          <t>강원도_정선군</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.boeun.go.kr/www/selectBbsNttList.do?bbsNo=66&amp;key=194&amp;pageIndex=1</t>
+          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D160" t="n">
         <v>3</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7359,12 +7367,12 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>경기 포천 육용종계농장 고병원성 조류인플루엔자 발생관련 가축(육용종계, 육계) 등에 대한 일시이동중지 명령 알림</t>
+          <t>주택건설사업계획 승인 고시 [SG아파트_세기건설(주)]</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -7416,16 +7424,16 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>강원도_정선군</t>
+          <t>강원도_춘천시</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://eminwon.jeongseon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05,06</t>
+          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D162" t="n">
         <v>3</v>
@@ -7449,7 +7457,7 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>주택건설사업계획 승인 고시 [SG아파트_세기건설(주)]</t>
+          <t>강촌분구 외 5개소 노후하수관로 정비사업 실시설계용역 사업 집행계획 및 사업수행능력평가서 제출안내 공고</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -7461,45 +7469,57 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>충청도_당진시</t>
+          <t>충청도_단양군</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
+          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>실패(타임아웃)</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>타임아웃</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026년 지적재조사사업 측량·조사 등의 위탁고시</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>충청도_증평군</t>
+          <t>충청도_진천군</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
+          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -7510,12 +7530,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7527,40 +7547,40 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>2026년 제1회 증평군 주소정보위원회 심의 결과 공고</t>
+          <t>『구암저수지 둘레길 조성사업』 신기술·특허공법 선정 공법제안서 제출안내 ...</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>충청도_단양군</t>
+          <t>충청도_서천군</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://eminwon.danyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -7572,28 +7592,28 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>2026년 지적재조사사업 측량·조사 등의 위탁고시</t>
+          <t>도로명주소 고시</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>강원도_춘천시</t>
+          <t>충청도_청양군</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.chuncheon.go.kr/cityhall/administrative-info/notice-info/notice-announcement/?pageIndex=5</t>
+          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D166" t="n">
         <v>3</v>
@@ -7617,7 +7637,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>강촌분구 외 5개소 노후하수관로 정비사업 실시설계용역 사업 집행계획 및 사업수행능력평가서 제출안내 공고</t>
+          <t>2026년 환경개선부담금 부과 관련 개인정보 제3자 위탁사항 알림</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -7629,16 +7649,16 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>충청도_진천군</t>
+          <t>충청도_당진시</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>http://eminwon.jincheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05,06</t>
+          <t>https://eminwon.dangjin.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D167" t="n">
         <v>3</v>
@@ -7662,40 +7682,40 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>『구암저수지 둘레길 조성사업』 신기술·특허공법 선정 공법제안서 제출안내 ...</t>
+          <t>2026년 소규모 공동주택 안전점검 용역 견적 제출 안내 공고</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>충청도_서천군</t>
+          <t>충청도_논산시</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://eminwon.seocheon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01&amp;list_gubun=</t>
+          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7707,28 +7727,28 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>도로명주소 고시</t>
+          <t>지적기준점(도근점) 성과고시(세계좌표 3점)</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>충청도_청주시_상당구</t>
+          <t>충청도_천안시</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
+          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D169" t="n">
         <v>3</v>
@@ -7752,7 +7772,7 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>학대피해아동쉼터 운영 수탁자 선정 심의결과 공고</t>
+          <t>「풍서천 재해복구사업(개선)」재난안전신기술 공법선정을 위한 기술제안서 제...</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -7764,16 +7784,16 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>충청도_천안시</t>
+          <t>충청도_청주시_상당구</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://eminwon.cheonan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,05&amp;epcCheck=Y&amp;recent_mm=60</t>
+          <t>https://eminwon.cheongju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;yyyy=2020</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D170" t="n">
         <v>3</v>
@@ -7797,7 +7817,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>「풍서천 재해복구사업(개선)」재난안전신기술 공법선정을 위한 기술제안서 제...</t>
+          <t>학대피해아동쉼터 운영 수탁자 선정 심의결과 공고</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -7854,16 +7874,16 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>충청도_논산시</t>
+          <t>충청도_아산시</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://eminwon.nonsan21.net/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,05,04,06</t>
+          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D172" t="n">
         <v>3</v>
@@ -7887,7 +7907,7 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>지적기준점(도근점) 성과고시(세계좌표 3점)</t>
+          <t>2026년 아산 국가유산 야행 행사대행 용역 제안서 평가결과 및 우선협상...</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -7899,23 +7919,23 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>충청도_아산시</t>
+          <t>충청도_태안군</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://eminwon.asan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04,06,07&amp;ofr_pageSize=10&amp;epcCheck=Y</t>
+          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7932,7 +7952,7 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>2026년 아산 국가유산 야행 행사대행 용역 제안서 평가결과 및 우선협상...</t>
+          <t>도로명주소 부여 고시 (3건)</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -8034,28 +8054,28 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>전라도_무주군</t>
+          <t>전라도_임실군</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
+          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -8067,28 +8087,28 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>용역[2025년도 수질오염 총량관리 이행평가 용역] 수의견적 공고</t>
+          <t>2026년 임실군 가로수 조성관리계획 고시</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>전라도_임실군</t>
+          <t>전라도_정읍시</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://eminwon.imsil.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D177" t="n">
         <v>3</v>
@@ -8112,7 +8132,7 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>2026년 임실군 가로수 조성관리계획 고시</t>
+          <t>칠보면 와우제 보수보강공사 긴급 입찰공고</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -8124,16 +8144,16 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>전라도_정읍시</t>
+          <t>전라도_목포시</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>http://eminwon.jeongeup.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07</t>
+          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D178" t="n">
         <v>3</v>
@@ -8157,7 +8177,7 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>칠보면 와우제 보수보강공사 긴급 입찰공고</t>
+          <t>공유수면 점용사용 변경허가 고시새로운글</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -8169,23 +8189,23 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>전라도_목포시</t>
+          <t>전라도_장흥군</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.mokpo.go.kr/www/mokpo_news/notification/public_notice?page=3</t>
+          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8202,35 +8222,35 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>공유수면 점용사용 변경허가 고시새로운글</t>
+          <t>「장흥 쓰레기위생매립장 침출수처리시설 개선사업」 침출수처리 공법..</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>전라도_장흥군</t>
+          <t>전라도_무주군</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.jangheung.go.kr/www/organization/news/notification</t>
+          <t>https://eminwon.muju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;subCheck=Y</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8247,12 +8267,12 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>「장흥 쓰레기위생매립장 침출수처리시설 개선사업」 침출수처리 공법..</t>
+          <t>2026년 무주군 보육정책위원회 심의결과 공고</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
@@ -8304,50 +8324,61 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>전라도_담양군</t>
+          <t>전라도_고흥군</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
+          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>실패(Alert Text: /eminwon/getSearch)</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Alert Text: /eminwon/getSearchList 페이징 오류
-Message: unexpected alert open: {Alert text : /eminwon/get</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>도로명주소 고시</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>전라도_고흥군</t>
+          <t>전라도_여수시</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.goheung.go.kr/contentsView.do?pageId=www99</t>
+          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=4</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D183" t="n">
         <v>3</v>
@@ -8371,7 +8402,7 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>도로명주소 고시</t>
+          <t>「2026 유엔기후변화협약 기후주간 행사개최 지원사업」 제안서 평가위원(...새로운글</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -8428,16 +8459,16 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>전라도_여수시</t>
+          <t>전라도_화순군</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.yeosu.go.kr/www/govt/news/notify?page=4</t>
+          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D185" t="n">
         <v>3</v>
@@ -8461,7 +8492,7 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>「2026 유엔기후변화협약 기후주간 행사개최 지원사업」 제안서 평가위원(...새로운글</t>
+          <t>제279회 화순군의회 임시회 부의 안건 공고</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -8473,23 +8504,23 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>경상도_포항시</t>
+          <t>경상도_봉화군</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
+          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8506,43 +8537,59 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>「포항시 투자유치 종합계획 수립 연구용역」제안서 평가위원(후보자) 모집 공고</t>
+          <t>2026년 봉화군가족센터 가사돌봄관리사 채용 공고(2차)</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>경상도_청송군</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>스킵(fail)</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>2025년 하반기 행정안전부 기구정원 관리실태 감사 결...</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8552,7 +8599,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
+          <t>https://www.cs.go.kr/news/00002679/00006203.web</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -8576,68 +8623,52 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>경상도_구미시</t>
+          <t>경상도_청송군</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
+          <t>https://www.cs.go.kr/news/00002679/00002687.web?upunit=50&amp;cpage=1</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>3</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>스킵(fail)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>「구미시 공공하수처리시설 수질TMS 유지관리 용역」제안서 평가위원(후보자) 모집 공고</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>경상도_포항시</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=156&amp;pageNo=1</t>
+          <t>https://www.pohang.go.kr/portal/saeol/gosi/list.do?mid=0202010000&amp;token=1702008153483</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D190" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8654,12 +8685,12 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>2025년 하반기 행정안전부 기구정원 관리실태 감사 결...</t>
+          <t>「포항시 투자유치 종합계획 수립 연구용역」제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
@@ -8695,23 +8726,23 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>경상도_산청군</t>
+          <t>경상도_구미시</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
+          <t>https://www.gumi.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mid=0401040000</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D192" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8728,35 +8759,35 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>2026년 산청군 맞춤형 진로진학 프로그램 제안서 평가(정성) 결과 공고</t>
+          <t>「구미시 공공하수처리시설 수질TMS 유지관리 용역」제안서 평가위원(후보자) 모집 공고</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>경상도_의성군</t>
+          <t>경상도_산청군</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=3</t>
+          <t>https://www.sancheong.go.kr/www/selectBbsNttList.do?bbsNo=118&amp;key=158&amp;pageUnit=90</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8773,7 +8804,7 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>2026년 소상공인 고효율기기 지원사업 공고</t>
+          <t>2026년 산청군 맞춤형 진로진학 프로그램 제안서 평가(정성) 결과 공고</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -8785,16 +8816,16 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>경상도_함양군</t>
+          <t>경상도_의성군</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
+          <t>https://www.usc.go.kr/ko/page.do?mnu_uid=157&amp;pageNo=4</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D194" t="n">
         <v>3</v>
@@ -8818,7 +8849,7 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>함양군 공공디자인 진흥계획 수립 용역 제안서 평가위원회 평가결과 공개</t>
+          <t>2026년 다함께돌봄센터 예산 공고</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -8830,23 +8861,23 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>대전시설관리공단</t>
+          <t>경상도_함양군</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.djsiseol.or.kr/portal/sub060301_list.asp</t>
+          <t>https://eminwon.hygn.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,06,07</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D195" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8856,18 +8887,14 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>�ѹ繮ȭü������ 2026�� 3�� ������Ŭ���� �ȳ�</t>
+          <t>함양군 공공디자인 진흥계획 수립 용역 제안서 평가위원회 평가결과 공개</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -8879,12 +8906,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>경상도_김천시</t>
+          <t>서울시설관리공단</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
+          <t>https://www.sisul.or.kr/open_content/main/bbs/bbsMsgList.do?bcd=specific&amp;listsz=10&amp;symd=&amp;eymd=&amp;keyfield=title&amp;keyword=</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -8897,12 +8924,12 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>실패(HTTP 0: 새 URL 탐색 실패)</t>
+          <t>실패(HTTP ?: 새 URL 탐색 실패)</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>HTTP 0: 새 URL 탐색 실패</t>
+          <t>HTTP ?: 새 URL 탐색 실패</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -8912,45 +8939,61 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>경상도_영주시</t>
+          <t>경기도_포천시</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
+          <t>https://www.pocheon.go.kr/www/selectEminwonList.do?key=12563&amp;notAncmtSeCode=01</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
-      </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>포천시 농업기술센터 공고 제2026-145호포천 고병원성AI 발생(축O종계장) 관련 방역대 내 농가 이동제한 및 소독명령</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>경기도_여주시</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://www.yeoju.go.kr/www/selectEminwonList.do?key=413&amp;pageIndex=1</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -8963,27 +9006,27 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>실패(URL 복구 후 파싱 실패: 테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>URL 복구 후 파싱 실패: 테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>경상도_영천시</t>
+          <t>경상도_김천시</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.yc.go.kr/portal/saeol/gosi/list.do?mId=0301040000</t>
+          <t>https://www.gc.go.kr/portal/saeol/gosi/list.do?seCode=01&amp;mId=1202180100</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -9011,61 +9054,45 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>강원도_홍천군</t>
+          <t>전라도_신안군</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.hongcheon.go.kr/www/selectEminwonList.do?key=278</t>
+          <t>https://www.shinan.go.kr/home/www/openinfo/participation_07/participation_07_04/page.wscms?page=1</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>지적측량기준점(도근점) 성과 고시</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>전라도_보성군</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.boseong.go.kr/www/open_administration/city_news/notification?page=1</t>
+          <t>https://www.yc.go.kr/portal/contents.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -9078,27 +9105,27 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>경상도_영주시</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
+          <t>https://www.yeongju.go.kr/open_content/main/page.do?mnu_uid=10619&amp;boardType=notice&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -9111,27 +9138,27 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>경상도_고령군</t>
+          <t>경상도_영천시</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.goryeong.go.kr/kor/boardList.do?IDX=154&amp;BRD_ID=1023</t>
+          <t>https://www.yc.go.kr/portal/contents.do?mId=0301040000</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -9159,12 +9186,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?BRD_ID=1023&amp;IDX=154</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -9177,27 +9204,27 @@
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>경상도_칠곡군</t>
+          <t>경상도_고령군</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
+          <t>https://www.goryeong.go.kr/kor/boardList.do?BRD_ID=1023&amp;IDX=154</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -9210,27 +9237,27 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>테이블 없음: tbody</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>경상도_고성군</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
+          <t>https://www.chilgok.go.kr/portal/saeol/gosi/list.do?mId=0201030000</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -9243,12 +9270,12 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>실패(URL 복구 후에도 접근 불가)</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>URL 복구 후에도 접근 불가</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -9258,12 +9285,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>경상도_진주시</t>
+          <t>경상도_칠곡군</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
+          <t>https://www.chilgok.go.kr/portal/bbs/list.do?ptIdx=111&amp;mId=0201010000</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -9276,12 +9303,12 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>실패(URL 복구 후 파싱 실패: 테이블 없음: div.li)</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>URL 복구 후 파싱 실패: 테이블 없음: div.list1f1t3i1</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -9291,12 +9318,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>경상도_울릉군</t>
+          <t>경상도_진주시</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
+          <t>https://www.jinju.go.kr/00130/02730/05586.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -9309,12 +9336,12 @@
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
+          <t>실패(URL 복구 후 파싱 실패: 테이블 없음: div.li)</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>테이블 없음: tbody</t>
+          <t>URL 복구 후 파싱 실패: 테이블 없음: div.list1f1t3i1</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -9324,12 +9351,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>경상도_창녕군</t>
+          <t>경상도_고성군</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
+          <t>https://www.goseong.go.kr/board/list.goseong?boardId=BBS_0000015&amp;menuCd=DOM_000000103001014000&amp;contentsSid=29&amp;cpath=&amp;startPage=1</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -9342,12 +9369,12 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>실패(URL 복구 후 파싱 실패: 테이블 없음: div.li)</t>
+          <t>실패(URL 복구 후에도 접근 불가)</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>URL 복구 후 파싱 실패: 테이블 없음: div.list1f1t3i1</t>
+          <t>URL 복구 후에도 접근 불가</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -9366,7 +9393,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D210" t="n">
         <v>1</v>
@@ -9406,61 +9433,45 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>경상도_안동시</t>
+          <t>경상도_창녕군</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.andong.go.kr/portal/contents.do?mId=0401020000</t>
+          <t>https://www.cng.go.kr/01541/01539/01553.web?&amp;cpage=1</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>2</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>자가치유성공</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>예안면 이장심사위원회 심의 결과 공고</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+          <t>실패(URL 복구 후 파싱 실패: 테이블 없음: div.li)</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>URL 복구 후 파싱 실패: 테이블 없음: div.list1f1t3i1</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>경상도_영덕군</t>
+          <t>경상도_안동시</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.yd.go.kr/?page_id=763</t>
+          <t>https://www.andong.go.kr/portal/saeol/gosi/list.do?mId=0401020100</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -9471,12 +9482,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -9492,24 +9503,24 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>남영덕 하이패스IC(고속국도 65호선) 추가설치 타당성조사 용역 제안서 평가위원(후보자) 모집 공고</t>
+          <t>예안면 이장심사위원회 심의 결과 공고</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>전라도_함평군</t>
+          <t>경상도_울릉군</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
+          <t>https://www.ulleung.go.kr/ko/page.do?pageNo=1&amp;mnu_uid=571</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -9522,10 +9533,14 @@
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr"/>
+          <t>실패(테이블 없음: tbody)</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>테이블 없음: tbody</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
@@ -9533,78 +9548,106 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>경기도_수원_영통구</t>
+          <t>경상도_영덕군</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
+          <t>https://www.yd.go.kr/?page_id=763</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
-      </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table.p-table.default )</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>테이블 없음: table.p-table.default tbody</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
+          <t>자가치유성공</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>남영덕 하이패스IC(고속국도 65호선) 추가설치 타당성조사 용역 제안서 평가위원(후보자) 모집 공고</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>경기도_용인시처인구</t>
+          <t>전라도_함평군</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://eminwon.yongin.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,04&amp;homepage_pbs_yn=Y&amp;subCheck=Y&amp;ofr_pageSize=10&amp;jndinm=OfrNotAncmtEJB&amp;context=NTIS&amp;list_gubun=&amp;epcCheck=Y;</t>
+          <t>https://www.hampyeong.go.kr/pg/GosiList.do?pageId=www273</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D215" t="n">
-        <v>0</v>
-      </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table.boardDefalut tbo)</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>테이블 없음: table.boardDefalut tbody tr</t>
-        </is>
-      </c>
+          <t>Zero-Selector성공</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>2023년 함평군 지적재조사사업 완료 공람·공고</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>충청도_청양군</t>
+          <t>경기도_수원_영통구</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://eminwon.cheongyang.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04,06&amp;list_gubun=A</t>
+          <t>https://eminwon.suwon.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04&amp;cgg_code=5610000&amp;epcCheck=Y</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -9617,12 +9660,12 @@
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+          <t>실패(테이블 없음: table.p-table.default )</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: table.p-table.default tbody</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -9632,12 +9675,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>충청도_태안군</t>
+          <t>경기도_성남시중원구</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>http://eminwon.taean.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05&amp;list_gubun=A</t>
+          <t>http://eminwon.seongnam.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?cgg_code=3800000&amp;not_ancmt_se_code=01,02,30,04,05,06&amp;recent_mm=12&amp;list_gubun=&amp;nodate_recent_mm=12</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -9650,12 +9693,12 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+          <t>실패(테이블 없음: table.bd00Bbs tbody tr)</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: table.bd00Bbs tbody tr</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -9665,30 +9708,38 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>전라도_전주시</t>
+          <t>충청도_증평군</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
+          <t>http://eminwon.jp.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,03,04,06&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
-      </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
+          <t>실패(테이블 없음: form &gt; table:nth-child)</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>테이블 없음: tbody</t>
+          <t>테이블 없음: form &gt; table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table &gt; tbody</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -9698,12 +9749,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>전라도_진안군</t>
+          <t>전라도_전주시</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
+          <t>https://eminwon.jeonju.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04&amp;epcCheck=Y&amp;recent_mm=60&amp;list_gubun=A</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -9716,12 +9767,12 @@
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -9731,30 +9782,38 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>전라도_나주시</t>
+          <t>전라도_익산시</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
+          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
-      </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: tbody)</t>
+          <t>실패(테이블 없음: table:nth-child(27) &gt; )</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>테이블 없음: tbody</t>
+          <t>테이블 없음: table:nth-child(27) &gt; tbody &gt; tr &gt; td &gt; table</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -9764,38 +9823,30 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>전라도_화순군</t>
+          <t>전라도_진안군</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://eminwon.hwasun.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,02,03,04,05,06,07&amp;epcCheck=Y</t>
+          <t>https://eminwon.jinan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;subcheck=Y</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>2</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
+          <t>실패(테이블 없음: table:nth-child(23) &gt; )</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: table:nth-child(23) &gt; tbody &gt; tr &gt; td &gt; table</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -9805,38 +9856,30 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>전라도_익산시</t>
+          <t>전라도_나주시</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://eminwon.iksan.go.kr/emwp/jsp/ofr/OfrNotAncmtLSub.jsp?not_ancmt_se_code=01,02,03,04,05&amp;cpath=</t>
+          <t>https://www.naju.go.kr/www/administration/notice/legislation?page=1</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>2</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(27) &gt; )</t>
+          <t>실패(테이블 없음: tbody)</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>테이블 없음: table:nth-child(27) &gt; tbody &gt; tr &gt; td &gt; table</t>
+          <t>테이블 없음: tbody</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -9846,12 +9889,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>경상도_경산시</t>
+          <t>전라도_담양군</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
+          <t>https://www.damyang.go.kr/eminwon/searchList?domainId=DOM_0000001&amp;contentsSid=2&amp;menuCd=DOM_000000190001002001&amp;boardType=special&amp;listType=01</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -9864,10 +9907,14 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
+          <t>실패(테이블 없음: #dev-listArea)</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>테이블 없음: #dev-listArea</t>
+        </is>
+      </c>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
@@ -9875,40 +9922,28 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>경상도_봉화군</t>
+          <t>경상도_경산시</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://eminwon.bonghwa.go.kr/emwp/jsp/ofr/OfrNotAncmtL.jsp?not_ancmt_se_code=01,04&amp;list_gubun=A</t>
+          <t>https://www.gbgs.go.kr/open_content/ko/page.do?mnu_uid=2160&amp;pageSize=90</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>실패(테이블 없음: table:nth-child(32) &gt; )</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>테이블 없음: table:nth-child(32) &gt; tbody &gt; tr &gt; td &gt; table</t>
-        </is>
-      </c>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
